--- a/BRIN 3219/Octubre/BRIN3219-EXPENSAS-Octubre.xlsx
+++ b/BRIN 3219/Octubre/BRIN3219-EXPENSAS-Octubre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BRIN 3219\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BRIN 3219\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A12A539-E23F-4F83-AC6F-24D5C58A4DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C17160-758B-48A0-95E0-73FE9D94A23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$N$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$98</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$101</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="158">
   <si>
     <t>U.F.</t>
   </si>
@@ -498,19 +498,25 @@
     <t>AYSA</t>
   </si>
   <si>
-    <t>Dr. Sarro Murillo escrito</t>
-  </si>
-  <si>
-    <t>VTO: 15/10</t>
-  </si>
-  <si>
-    <t>SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>Damato fumigaciones - SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>Egresos por gastos mes - SEPTIEMBRE</t>
+    <t>VTO: 14/11</t>
+  </si>
+  <si>
+    <t>OCTUBRE</t>
+  </si>
+  <si>
+    <t>Damato fumigaciones - OCTUBRE</t>
+  </si>
+  <si>
+    <t>Egresos por gastos mes - OCTUBRE</t>
+  </si>
+  <si>
+    <t>Citta Cerrajeria - Cierre defectuoso de puerta principal</t>
+  </si>
+  <si>
+    <t>Destapacion AYSA - 31/10</t>
+  </si>
+  <si>
+    <t>Julio Doartero - Arreglo cisterna - 30/10</t>
   </si>
 </sst>
 </file>
@@ -527,7 +533,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -732,6 +738,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1312,7 +1325,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1603,160 +1616,174 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="16" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="30" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="10" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="30" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="30" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2203,7 +2230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -2228,23 +2255,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="184"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="186"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="216"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="215">
+      <c r="E3" s="190">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="215"/>
-      <c r="G3" s="215"/>
-      <c r="H3" s="216"/>
+      <c r="F3" s="190"/>
+      <c r="G3" s="190"/>
+      <c r="H3" s="191"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2291,10 +2318,10 @@
         <v>67</v>
       </c>
       <c r="F8" s="90" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -2323,14 +2350,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="193"/>
-      <c r="B12" s="194"/>
-      <c r="C12" s="194"/>
-      <c r="D12" s="194"/>
-      <c r="E12" s="194"/>
-      <c r="F12" s="194"/>
-      <c r="G12" s="194"/>
-      <c r="H12" s="195"/>
+      <c r="A12" s="222"/>
+      <c r="B12" s="183"/>
+      <c r="C12" s="183"/>
+      <c r="D12" s="183"/>
+      <c r="E12" s="183"/>
+      <c r="F12" s="183"/>
+      <c r="G12" s="183"/>
+      <c r="H12" s="223"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2343,19 +2370,19 @@
       <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:9" ht="15.75">
-      <c r="A14" s="219" t="s">
+      <c r="A14" s="196" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="219"/>
-      <c r="C14" s="219"/>
-      <c r="D14" s="219"/>
-      <c r="E14" s="219"/>
-      <c r="F14" s="219"/>
-      <c r="G14" s="219"/>
-      <c r="H14" s="219"/>
+      <c r="B14" s="196"/>
+      <c r="C14" s="196"/>
+      <c r="D14" s="196"/>
+      <c r="E14" s="196"/>
+      <c r="F14" s="196"/>
+      <c r="G14" s="196"/>
+      <c r="H14" s="196"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="227" t="s">
+      <c r="A15" s="178" t="s">
         <v>149</v>
       </c>
       <c r="B15" s="141"/>
@@ -2364,12 +2391,12 @@
       <c r="E15" s="141"/>
       <c r="F15" s="141"/>
       <c r="G15" s="141"/>
-      <c r="H15" s="74">
-        <v>324630.59999999998</v>
+      <c r="H15" s="230">
+        <v>381604.3</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="227" t="s">
+      <c r="A16" s="178" t="s">
         <v>89</v>
       </c>
       <c r="B16" s="141"/>
@@ -2378,13 +2405,13 @@
       <c r="E16" s="141"/>
       <c r="F16" s="141"/>
       <c r="G16" s="141"/>
-      <c r="H16" s="74">
-        <v>-51129.33</v>
+      <c r="H16" s="230">
+        <v>-60102.67</v>
       </c>
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="227" t="s">
+      <c r="A17" s="178" t="s">
         <v>122</v>
       </c>
       <c r="B17" s="141"/>
@@ -2393,13 +2420,13 @@
       <c r="E17" s="141"/>
       <c r="F17" s="141"/>
       <c r="G17" s="141"/>
-      <c r="H17" s="74">
-        <v>0.73</v>
+      <c r="H17" s="230">
+        <v>0.37</v>
       </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="227" t="s">
+      <c r="A18" s="178" t="s">
         <v>75</v>
       </c>
       <c r="B18" s="141"/>
@@ -2408,26 +2435,26 @@
       <c r="E18" s="141"/>
       <c r="F18" s="141"/>
       <c r="G18" s="141"/>
-      <c r="H18" s="74">
+      <c r="H18" s="70">
         <f>SUM(H15:H17)</f>
-        <v>273501.99999999994</v>
+        <v>321502</v>
       </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" ht="0.75" customHeight="1">
-      <c r="A19" s="228" t="s">
+      <c r="A19" s="218" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="228"/>
-      <c r="C19" s="228"/>
-      <c r="D19" s="228"/>
-      <c r="E19" s="228"/>
-      <c r="F19" s="228"/>
-      <c r="G19" s="228"/>
-      <c r="H19" s="228"/>
+      <c r="B19" s="218"/>
+      <c r="C19" s="218"/>
+      <c r="D19" s="218"/>
+      <c r="E19" s="218"/>
+      <c r="F19" s="218"/>
+      <c r="G19" s="218"/>
+      <c r="H19" s="218"/>
     </row>
     <row r="20" spans="1:9" hidden="1">
-      <c r="A20" s="227" t="s">
+      <c r="A20" s="178" t="s">
         <v>132</v>
       </c>
       <c r="B20" s="141"/>
@@ -2439,7 +2466,7 @@
       <c r="H20" s="74"/>
     </row>
     <row r="21" spans="1:9" hidden="1">
-      <c r="A21" s="227"/>
+      <c r="A21" s="178"/>
       <c r="B21" s="141"/>
       <c r="C21" s="141"/>
       <c r="D21" s="141"/>
@@ -2451,7 +2478,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" hidden="1">
-      <c r="A22" s="227"/>
+      <c r="A22" s="178"/>
       <c r="B22" s="141"/>
       <c r="C22" s="141"/>
       <c r="D22" s="141"/>
@@ -2463,7 +2490,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" hidden="1">
-      <c r="A23" s="227"/>
+      <c r="A23" s="178"/>
       <c r="B23" s="141"/>
       <c r="C23" s="141"/>
       <c r="D23" s="141"/>
@@ -2475,7 +2502,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" hidden="1">
-      <c r="A24" s="227" t="s">
+      <c r="A24" s="178" t="s">
         <v>133</v>
       </c>
       <c r="B24" s="141"/>
@@ -2487,7 +2514,7 @@
       <c r="H24" s="74"/>
     </row>
     <row r="25" spans="1:9" hidden="1">
-      <c r="A25" s="227" t="s">
+      <c r="A25" s="178" t="s">
         <v>89</v>
       </c>
       <c r="B25" s="141"/>
@@ -2499,7 +2526,7 @@
       <c r="H25" s="74"/>
     </row>
     <row r="26" spans="1:9" hidden="1">
-      <c r="A26" s="227" t="s">
+      <c r="A26" s="178" t="s">
         <v>75</v>
       </c>
       <c r="B26" s="141"/>
@@ -2514,16 +2541,16 @@
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="229" t="s">
+      <c r="A27" s="217" t="s">
         <v>136</v>
       </c>
-      <c r="B27" s="229"/>
-      <c r="C27" s="229"/>
-      <c r="D27" s="229"/>
-      <c r="E27" s="229"/>
-      <c r="F27" s="229"/>
-      <c r="G27" s="229"/>
-      <c r="H27" s="229"/>
+      <c r="B27" s="217"/>
+      <c r="C27" s="217"/>
+      <c r="D27" s="217"/>
+      <c r="E27" s="217"/>
+      <c r="F27" s="217"/>
+      <c r="G27" s="217"/>
+      <c r="H27" s="217"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="141" t="s">
@@ -2535,7 +2562,7 @@
       <c r="E28" s="141"/>
       <c r="F28" s="141"/>
       <c r="G28" s="141"/>
-      <c r="H28" s="74">
+      <c r="H28" s="230">
         <v>32000</v>
       </c>
     </row>
@@ -2559,25 +2586,25 @@
       <c r="E30" s="141"/>
       <c r="F30" s="141"/>
       <c r="G30" s="141"/>
-      <c r="H30" s="74">
+      <c r="H30" s="70">
         <f>SUM(H28:H29)</f>
         <v>32000</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A31" s="230" t="s">
+      <c r="A31" s="197" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="230"/>
-      <c r="C31" s="230"/>
-      <c r="D31" s="230"/>
-      <c r="E31" s="230"/>
-      <c r="F31" s="230"/>
-      <c r="G31" s="230"/>
-      <c r="H31" s="230"/>
+      <c r="B31" s="197"/>
+      <c r="C31" s="197"/>
+      <c r="D31" s="197"/>
+      <c r="E31" s="197"/>
+      <c r="F31" s="197"/>
+      <c r="G31" s="197"/>
+      <c r="H31" s="197"/>
     </row>
     <row r="32" spans="1:9" hidden="1">
-      <c r="A32" s="227"/>
+      <c r="A32" s="178"/>
       <c r="B32" s="141"/>
       <c r="C32" s="141"/>
       <c r="D32" s="141"/>
@@ -2587,18 +2614,18 @@
       <c r="H32" s="74"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="227" t="s">
+      <c r="A33" s="178" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="231"/>
+      <c r="B33" s="179"/>
       <c r="C33" s="141"/>
       <c r="D33" s="141"/>
       <c r="E33" s="141"/>
       <c r="F33" s="141"/>
       <c r="G33" s="141"/>
-      <c r="H33" s="74">
-        <f>14146.69+1571.86+33034.56</f>
-        <v>48753.11</v>
+      <c r="H33" s="230">
+        <f>1623.15+33810.99+14068.38</f>
+        <v>49502.52</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2625,22 +2652,22 @@
       <c r="E35" s="141"/>
       <c r="F35" s="141"/>
       <c r="G35" s="141"/>
-      <c r="H35" s="74">
+      <c r="H35" s="70">
         <f>SUM(H32:H34)</f>
-        <v>48753.11</v>
+        <v>49502.52</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="230" t="s">
+      <c r="A36" s="197" t="s">
         <v>137</v>
       </c>
-      <c r="B36" s="230"/>
-      <c r="C36" s="230"/>
-      <c r="D36" s="230"/>
-      <c r="E36" s="230"/>
-      <c r="F36" s="230"/>
-      <c r="G36" s="230"/>
-      <c r="H36" s="230"/>
+      <c r="B36" s="197"/>
+      <c r="C36" s="197"/>
+      <c r="D36" s="197"/>
+      <c r="E36" s="197"/>
+      <c r="F36" s="197"/>
+      <c r="G36" s="197"/>
+      <c r="H36" s="197"/>
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1">
       <c r="A37" s="141" t="s">
@@ -2652,12 +2679,12 @@
       <c r="E37" s="141"/>
       <c r="F37" s="141"/>
       <c r="G37" s="141"/>
-      <c r="H37" s="74">
+      <c r="H37" s="230">
         <v>2056747.63</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="232" t="s">
+      <c r="A38" s="180" t="s">
         <v>102</v>
       </c>
       <c r="B38" s="141"/>
@@ -2666,8 +2693,8 @@
       <c r="E38" s="141"/>
       <c r="F38" s="141"/>
       <c r="G38" s="141"/>
-      <c r="H38" s="74">
-        <v>50162.18</v>
+      <c r="H38" s="230">
+        <v>56106.559999999998</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2680,22 +2707,22 @@
       <c r="E39" s="141"/>
       <c r="F39" s="141"/>
       <c r="G39" s="141"/>
-      <c r="H39" s="145">
+      <c r="H39" s="181">
         <f>SUM(H37:H38)</f>
-        <v>2106909.81</v>
+        <v>2112854.19</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="219" t="s">
+      <c r="A40" s="196" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="219"/>
-      <c r="C40" s="219"/>
-      <c r="D40" s="219"/>
-      <c r="E40" s="219"/>
-      <c r="F40" s="219"/>
-      <c r="G40" s="219"/>
-      <c r="H40" s="219"/>
+      <c r="B40" s="196"/>
+      <c r="C40" s="196"/>
+      <c r="D40" s="196"/>
+      <c r="E40" s="196"/>
+      <c r="F40" s="196"/>
+      <c r="G40" s="196"/>
+      <c r="H40" s="196"/>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="81" t="s">
@@ -2707,8 +2734,8 @@
       <c r="E41" s="141"/>
       <c r="F41" s="141"/>
       <c r="G41" s="141"/>
-      <c r="H41" s="74">
-        <v>71200</v>
+      <c r="H41" s="230">
+        <v>77500</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2721,13 +2748,13 @@
       <c r="E42" s="141"/>
       <c r="F42" s="141"/>
       <c r="G42" s="141"/>
-      <c r="H42" s="74">
-        <v>20417</v>
+      <c r="H42" s="230">
+        <v>20774.91</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="141" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B43" s="141"/>
       <c r="C43" s="141"/>
@@ -2735,13 +2762,13 @@
       <c r="E43" s="141"/>
       <c r="F43" s="141"/>
       <c r="G43" s="141"/>
-      <c r="H43" s="74">
+      <c r="H43" s="230">
         <v>65000</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="141" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B44" s="141"/>
       <c r="C44" s="141"/>
@@ -2749,14 +2776,13 @@
       <c r="E44" s="141"/>
       <c r="F44" s="141"/>
       <c r="G44" s="141"/>
-      <c r="H44" s="74">
-        <v>33150</v>
-      </c>
-      <c r="J44" s="6"/>
+      <c r="H44" s="230">
+        <v>50000</v>
+      </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="141" t="s">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="B45" s="141"/>
       <c r="C45" s="141"/>
@@ -2764,26 +2790,27 @@
       <c r="E45" s="141"/>
       <c r="F45" s="141"/>
       <c r="G45" s="141"/>
-      <c r="H45" s="70">
-        <f>SUM(H41:H44)</f>
-        <v>189767</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="219" t="s">
-        <v>139</v>
-      </c>
-      <c r="B46" s="219"/>
-      <c r="C46" s="219"/>
-      <c r="D46" s="219"/>
-      <c r="E46" s="219"/>
-      <c r="F46" s="219"/>
-      <c r="G46" s="219"/>
-      <c r="H46" s="219"/>
+      <c r="H45" s="230">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A46" s="141" t="s">
+        <v>155</v>
+      </c>
+      <c r="B46" s="141"/>
+      <c r="C46" s="141"/>
+      <c r="D46" s="141"/>
+      <c r="E46" s="141"/>
+      <c r="F46" s="141"/>
+      <c r="G46" s="141"/>
+      <c r="H46" s="230">
+        <v>45000</v>
+      </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="141" t="s">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="B47" s="141"/>
       <c r="C47" s="141"/>
@@ -2791,16 +2818,14 @@
       <c r="E47" s="141"/>
       <c r="F47" s="141"/>
       <c r="G47" s="141"/>
-      <c r="H47" s="74">
-        <v>148100</v>
-      </c>
-      <c r="J47" t="s">
-        <v>148</v>
-      </c>
+      <c r="H47" s="230">
+        <v>50050</v>
+      </c>
+      <c r="J47" s="6"/>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="141" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="B48" s="141"/>
       <c r="C48" s="141"/>
@@ -2808,23 +2833,26 @@
       <c r="E48" s="141"/>
       <c r="F48" s="141"/>
       <c r="G48" s="141"/>
-      <c r="H48" s="74">
-        <v>30000</v>
+      <c r="H48" s="70">
+        <f>SUM(H41:H47)</f>
+        <v>368324.91000000003</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="141"/>
-      <c r="B49" s="141"/>
-      <c r="C49" s="141"/>
-      <c r="D49" s="141"/>
-      <c r="E49" s="141"/>
-      <c r="F49" s="141"/>
-      <c r="G49" s="141"/>
-      <c r="H49" s="74"/>
+      <c r="A49" s="196" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="196"/>
+      <c r="C49" s="196"/>
+      <c r="D49" s="196"/>
+      <c r="E49" s="196"/>
+      <c r="F49" s="196"/>
+      <c r="G49" s="196"/>
+      <c r="H49" s="196"/>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="141" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B50" s="141"/>
       <c r="C50" s="141"/>
@@ -2832,69 +2860,68 @@
       <c r="E50" s="141"/>
       <c r="F50" s="141"/>
       <c r="G50" s="141"/>
-      <c r="H50" s="233">
-        <f>SUM(H47:H49)</f>
-        <v>178100</v>
-      </c>
-      <c r="K50" s="7"/>
-    </row>
-    <row r="51" spans="1:11" s="6" customFormat="1">
-      <c r="A51" s="220" t="s">
+      <c r="H50" s="230">
+        <v>156900</v>
+      </c>
+      <c r="J50" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="141" t="s">
+        <v>121</v>
+      </c>
+      <c r="B51" s="141"/>
+      <c r="C51" s="141"/>
+      <c r="D51" s="141"/>
+      <c r="E51" s="141"/>
+      <c r="F51" s="141"/>
+      <c r="G51" s="141"/>
+      <c r="H51" s="230">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="141"/>
+      <c r="B52" s="141"/>
+      <c r="C52" s="141"/>
+      <c r="D52" s="141"/>
+      <c r="E52" s="141"/>
+      <c r="F52" s="141"/>
+      <c r="G52" s="141"/>
+      <c r="H52" s="74"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="141" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" s="141"/>
+      <c r="C53" s="141"/>
+      <c r="D53" s="141"/>
+      <c r="E53" s="141"/>
+      <c r="F53" s="141"/>
+      <c r="G53" s="141"/>
+      <c r="H53" s="181">
+        <f>SUM(H50:H52)</f>
+        <v>191900</v>
+      </c>
+      <c r="K53" s="7"/>
+    </row>
+    <row r="54" spans="1:11" s="6" customFormat="1">
+      <c r="A54" s="198" t="s">
         <v>140</v>
       </c>
-      <c r="B51" s="221"/>
-      <c r="C51" s="221"/>
-      <c r="D51" s="221"/>
-      <c r="E51" s="221"/>
-      <c r="F51" s="221"/>
-      <c r="G51" s="221"/>
-      <c r="H51" s="222"/>
-    </row>
-    <row r="52" spans="1:11" s="6" customFormat="1">
-      <c r="A52" s="81" t="s">
-        <v>123</v>
-      </c>
-      <c r="B52" s="81"/>
-      <c r="C52" s="81"/>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
-      <c r="H52" s="74">
-        <v>23006</v>
-      </c>
-      <c r="I52" s="60"/>
-    </row>
-    <row r="53" spans="1:11" s="6" customFormat="1">
-      <c r="A53" s="81" t="s">
-        <v>75</v>
-      </c>
-      <c r="B53" s="81"/>
-      <c r="C53" s="81"/>
-      <c r="D53" s="81"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="81"/>
-      <c r="G53" s="81"/>
-      <c r="H53" s="70">
-        <f>SUM(H52)</f>
-        <v>23006</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" s="6" customFormat="1">
-      <c r="A54" s="219" t="s">
-        <v>141</v>
-      </c>
-      <c r="B54" s="219"/>
-      <c r="C54" s="219"/>
-      <c r="D54" s="219"/>
-      <c r="E54" s="219"/>
-      <c r="F54" s="219"/>
-      <c r="G54" s="219"/>
-      <c r="H54" s="219"/>
+      <c r="B54" s="199"/>
+      <c r="C54" s="199"/>
+      <c r="D54" s="199"/>
+      <c r="E54" s="199"/>
+      <c r="F54" s="199"/>
+      <c r="G54" s="199"/>
+      <c r="H54" s="200"/>
     </row>
     <row r="55" spans="1:11" s="6" customFormat="1">
       <c r="A55" s="81" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="B55" s="81"/>
       <c r="C55" s="81"/>
@@ -2902,433 +2929,424 @@
       <c r="E55" s="81"/>
       <c r="F55" s="81"/>
       <c r="G55" s="81"/>
-      <c r="H55" s="74">
-        <v>90000</v>
-      </c>
+      <c r="H55" s="230">
+        <v>24990</v>
+      </c>
+      <c r="I55" s="60"/>
     </row>
     <row r="56" spans="1:11" s="6" customFormat="1">
-      <c r="A56" s="177"/>
-      <c r="B56" s="177"/>
-      <c r="C56" s="177"/>
-      <c r="D56" s="177"/>
-      <c r="E56" s="177"/>
-      <c r="F56" s="177"/>
-      <c r="G56" s="177"/>
-      <c r="H56" s="176"/>
+      <c r="A56" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="B56" s="81"/>
+      <c r="C56" s="81"/>
+      <c r="D56" s="81"/>
+      <c r="E56" s="81"/>
+      <c r="F56" s="81"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="70">
+        <f>SUM(H55)</f>
+        <v>24990</v>
+      </c>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1">
-      <c r="A57" s="177"/>
-      <c r="B57" s="177"/>
-      <c r="C57" s="177"/>
-      <c r="D57" s="177"/>
-      <c r="E57" s="177"/>
-      <c r="F57" s="177"/>
-      <c r="G57" s="177"/>
-      <c r="H57" s="176">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A58" s="81" t="s">
-        <v>76</v>
-      </c>
+      <c r="A57" s="196" t="s">
+        <v>141</v>
+      </c>
+      <c r="B57" s="196"/>
+      <c r="C57" s="196"/>
+      <c r="D57" s="196"/>
+      <c r="E57" s="196"/>
+      <c r="F57" s="196"/>
+      <c r="G57" s="196"/>
+      <c r="H57" s="196"/>
+    </row>
+    <row r="58" spans="1:11" s="6" customFormat="1">
+      <c r="A58" s="81"/>
       <c r="B58" s="81"/>
       <c r="C58" s="81"/>
       <c r="D58" s="81"/>
       <c r="E58" s="81"/>
       <c r="F58" s="81"/>
       <c r="G58" s="81"/>
-      <c r="H58" s="70">
-        <f>SUM(H55:H57)</f>
-        <v>90000</v>
-      </c>
-      <c r="I58" s="60"/>
-    </row>
-    <row r="59" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A59" s="220"/>
-      <c r="B59" s="221"/>
-      <c r="C59" s="221"/>
-      <c r="D59" s="221"/>
-      <c r="E59" s="221"/>
-      <c r="F59" s="221"/>
-      <c r="G59" s="221"/>
-      <c r="H59" s="222"/>
-    </row>
-    <row r="60" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A60" s="82"/>
-      <c r="B60" s="83"/>
-      <c r="C60" s="83"/>
-      <c r="D60" s="83"/>
-      <c r="E60" s="83"/>
-      <c r="F60" s="83"/>
-      <c r="G60" s="83"/>
-      <c r="H60" s="160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A61" s="161"/>
-      <c r="B61" s="162"/>
-      <c r="C61" s="162"/>
-      <c r="D61" s="162"/>
-      <c r="E61" s="162"/>
-      <c r="F61" s="162"/>
-      <c r="G61" s="162"/>
-      <c r="H61" s="163">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A62" s="164"/>
-      <c r="B62" s="165"/>
-      <c r="C62" s="165"/>
-      <c r="D62" s="165"/>
-      <c r="E62" s="165"/>
-      <c r="F62" s="165"/>
-      <c r="G62" s="165"/>
-      <c r="H62" s="160">
-        <f>H60+H61</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A63" s="201" t="s">
+      <c r="H58" s="74"/>
+    </row>
+    <row r="59" spans="1:11" s="6" customFormat="1">
+      <c r="A59" s="177"/>
+      <c r="B59" s="177"/>
+      <c r="C59" s="177"/>
+      <c r="D59" s="177"/>
+      <c r="E59" s="177"/>
+      <c r="F59" s="177"/>
+      <c r="G59" s="177"/>
+      <c r="H59" s="176"/>
+    </row>
+    <row r="60" spans="1:11" s="6" customFormat="1">
+      <c r="A60" s="177"/>
+      <c r="B60" s="177"/>
+      <c r="C60" s="177"/>
+      <c r="D60" s="177"/>
+      <c r="E60" s="177"/>
+      <c r="F60" s="177"/>
+      <c r="G60" s="177"/>
+      <c r="H60" s="176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A61" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="B61" s="81"/>
+      <c r="C61" s="81"/>
+      <c r="D61" s="81"/>
+      <c r="E61" s="81"/>
+      <c r="F61" s="81"/>
+      <c r="G61" s="81"/>
+      <c r="H61" s="70">
+        <f>SUM(H58:H60)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="60"/>
+    </row>
+    <row r="62" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A62" s="198"/>
+      <c r="B62" s="199"/>
+      <c r="C62" s="199"/>
+      <c r="D62" s="199"/>
+      <c r="E62" s="199"/>
+      <c r="F62" s="199"/>
+      <c r="G62" s="199"/>
+      <c r="H62" s="200"/>
+    </row>
+    <row r="63" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A63" s="82"/>
+      <c r="B63" s="83"/>
+      <c r="C63" s="83"/>
+      <c r="D63" s="83"/>
+      <c r="E63" s="83"/>
+      <c r="F63" s="83"/>
+      <c r="G63" s="83"/>
+      <c r="H63" s="160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A64" s="161"/>
+      <c r="B64" s="162"/>
+      <c r="C64" s="162"/>
+      <c r="D64" s="162"/>
+      <c r="E64" s="162"/>
+      <c r="F64" s="162"/>
+      <c r="G64" s="162"/>
+      <c r="H64" s="163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A65" s="164"/>
+      <c r="B65" s="165"/>
+      <c r="C65" s="165"/>
+      <c r="D65" s="165"/>
+      <c r="E65" s="165"/>
+      <c r="F65" s="165"/>
+      <c r="G65" s="165"/>
+      <c r="H65" s="160">
+        <f>H63+H64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A66" s="209" t="s">
         <v>84</v>
       </c>
-      <c r="B63" s="202"/>
-      <c r="C63" s="202"/>
-      <c r="D63" s="202"/>
-      <c r="E63" s="202"/>
-      <c r="F63" s="202"/>
-      <c r="G63" s="202"/>
-      <c r="H63" s="166">
-        <f>H58</f>
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A64" s="206"/>
-      <c r="B64" s="206"/>
-      <c r="C64" s="206"/>
-      <c r="D64" s="206"/>
-      <c r="E64" s="206"/>
-      <c r="F64" s="206"/>
-      <c r="G64" s="206"/>
-      <c r="H64" s="206"/>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A65" s="207"/>
-      <c r="B65" s="207"/>
-      <c r="C65" s="207"/>
-      <c r="D65" s="207"/>
-      <c r="E65" s="207"/>
-      <c r="F65" s="207"/>
-      <c r="G65" s="207"/>
-      <c r="H65" s="207"/>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A66" s="205" t="s">
+      <c r="B66" s="210"/>
+      <c r="C66" s="210"/>
+      <c r="D66" s="210"/>
+      <c r="E66" s="210"/>
+      <c r="F66" s="210"/>
+      <c r="G66" s="210"/>
+      <c r="H66" s="166">
+        <f>H61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A67" s="212"/>
+      <c r="B67" s="212"/>
+      <c r="C67" s="212"/>
+      <c r="D67" s="212"/>
+      <c r="E67" s="212"/>
+      <c r="F67" s="212"/>
+      <c r="G67" s="212"/>
+      <c r="H67" s="212"/>
+    </row>
+    <row r="68" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A68" s="213"/>
+      <c r="B68" s="213"/>
+      <c r="C68" s="213"/>
+      <c r="D68" s="213"/>
+      <c r="E68" s="213"/>
+      <c r="F68" s="213"/>
+      <c r="G68" s="213"/>
+      <c r="H68" s="213"/>
+    </row>
+    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A69" s="211" t="s">
         <v>86</v>
       </c>
-      <c r="B66" s="205"/>
-      <c r="C66" s="205"/>
-      <c r="D66" s="205"/>
-      <c r="E66" s="205"/>
-      <c r="F66" s="205"/>
-      <c r="G66" s="205"/>
-      <c r="H66" s="167"/>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A67" s="190"/>
-      <c r="B67" s="191"/>
-      <c r="C67" s="191"/>
-      <c r="D67" s="191"/>
-      <c r="E67" s="191"/>
-      <c r="F67" s="191"/>
-      <c r="G67" s="192"/>
-      <c r="H67" s="74"/>
-    </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A68" s="131" t="s">
+      <c r="B69" s="211"/>
+      <c r="C69" s="211"/>
+      <c r="D69" s="211"/>
+      <c r="E69" s="211"/>
+      <c r="F69" s="211"/>
+      <c r="G69" s="211"/>
+      <c r="H69" s="167"/>
+    </row>
+    <row r="70" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A70" s="219"/>
+      <c r="B70" s="220"/>
+      <c r="C70" s="220"/>
+      <c r="D70" s="220"/>
+      <c r="E70" s="220"/>
+      <c r="F70" s="220"/>
+      <c r="G70" s="221"/>
+      <c r="H70" s="74"/>
+    </row>
+    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A71" s="131" t="s">
         <v>75</v>
       </c>
-      <c r="B68" s="81"/>
-      <c r="C68" s="81"/>
-      <c r="D68" s="81"/>
-      <c r="E68" s="81"/>
-      <c r="F68" s="81"/>
-      <c r="G68" s="81"/>
-      <c r="H68" s="70">
-        <f>SUM(H67:H67)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A69" s="132"/>
-      <c r="B69" s="132"/>
-      <c r="C69" s="132"/>
-      <c r="D69" s="132"/>
-      <c r="E69" s="132"/>
-      <c r="F69" s="132"/>
-      <c r="G69" s="132"/>
-      <c r="H69" s="133"/>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A70" s="203" t="s">
+      <c r="B71" s="81"/>
+      <c r="C71" s="81"/>
+      <c r="D71" s="81"/>
+      <c r="E71" s="81"/>
+      <c r="F71" s="81"/>
+      <c r="G71" s="81"/>
+      <c r="H71" s="70">
+        <f>SUM(H70:H70)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A72" s="132"/>
+      <c r="B72" s="132"/>
+      <c r="C72" s="132"/>
+      <c r="D72" s="132"/>
+      <c r="E72" s="132"/>
+      <c r="F72" s="132"/>
+      <c r="G72" s="132"/>
+      <c r="H72" s="133"/>
+    </row>
+    <row r="73" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A73" s="192" t="s">
         <v>85</v>
       </c>
-      <c r="B70" s="204"/>
-      <c r="C70" s="204"/>
-      <c r="D70" s="204"/>
-      <c r="E70" s="204"/>
-      <c r="F70" s="204"/>
-      <c r="G70" s="204"/>
-      <c r="H70" s="134">
-        <f>H68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A71" s="187" t="s">
+      <c r="B73" s="193"/>
+      <c r="C73" s="193"/>
+      <c r="D73" s="193"/>
+      <c r="E73" s="193"/>
+      <c r="F73" s="193"/>
+      <c r="G73" s="193"/>
+      <c r="H73" s="134">
+        <f>H71</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A74" s="204" t="s">
         <v>91</v>
       </c>
-      <c r="B71" s="188"/>
-      <c r="C71" s="188"/>
-      <c r="D71" s="188"/>
-      <c r="E71" s="188"/>
-      <c r="F71" s="188"/>
-      <c r="G71" s="189"/>
-      <c r="H71" s="134"/>
-    </row>
-    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A72" s="187" t="s">
+      <c r="B74" s="205"/>
+      <c r="C74" s="205"/>
+      <c r="D74" s="205"/>
+      <c r="E74" s="205"/>
+      <c r="F74" s="205"/>
+      <c r="G74" s="206"/>
+      <c r="H74" s="134"/>
+    </row>
+    <row r="75" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A75" s="204" t="s">
         <v>96</v>
       </c>
-      <c r="B72" s="188"/>
-      <c r="C72" s="188"/>
-      <c r="D72" s="188"/>
-      <c r="E72" s="188"/>
-      <c r="F72" s="188"/>
-      <c r="G72" s="189"/>
-      <c r="H72" s="134"/>
-    </row>
-    <row r="73" spans="1:11" ht="18.75">
-      <c r="A73" s="203" t="s">
+      <c r="B75" s="205"/>
+      <c r="C75" s="205"/>
+      <c r="D75" s="205"/>
+      <c r="E75" s="205"/>
+      <c r="F75" s="205"/>
+      <c r="G75" s="206"/>
+      <c r="H75" s="134"/>
+    </row>
+    <row r="76" spans="1:11" ht="18.75">
+      <c r="A76" s="192" t="s">
         <v>92</v>
       </c>
-      <c r="B73" s="204"/>
-      <c r="C73" s="204"/>
-      <c r="D73" s="204"/>
-      <c r="E73" s="204"/>
-      <c r="F73" s="204"/>
-      <c r="G73" s="204"/>
-      <c r="H73" s="134">
-        <f>H30+H39+H45+H50+H53+H35+H18+H26</f>
-        <v>2852037.92</v>
-      </c>
-      <c r="J73" s="175"/>
-      <c r="K73" s="146"/>
-    </row>
-    <row r="74" spans="1:11" ht="18.75">
-      <c r="A74" s="196" t="s">
+      <c r="B76" s="193"/>
+      <c r="C76" s="193"/>
+      <c r="D76" s="193"/>
+      <c r="E76" s="193"/>
+      <c r="F76" s="193"/>
+      <c r="G76" s="193"/>
+      <c r="H76" s="134">
+        <f>H30+H39+H48+H53+H56+H35+H18+H26</f>
+        <v>3101073.62</v>
+      </c>
+      <c r="J76" s="175"/>
+      <c r="K76" s="146"/>
+    </row>
+    <row r="77" spans="1:11" ht="18.75">
+      <c r="A77" s="201" t="s">
         <v>126</v>
       </c>
-      <c r="B74" s="197"/>
-      <c r="C74" s="197"/>
-      <c r="D74" s="197"/>
-      <c r="E74" s="197"/>
-      <c r="F74" s="197"/>
-      <c r="G74" s="198"/>
-      <c r="H74" s="135">
-        <f>H71+H73</f>
-        <v>2852037.92</v>
-      </c>
-      <c r="I74" s="130"/>
-      <c r="J74" s="208"/>
-      <c r="K74" s="208"/>
-    </row>
-    <row r="75" spans="1:11" ht="18.75">
-      <c r="A75" s="196" t="s">
+      <c r="B77" s="202"/>
+      <c r="C77" s="202"/>
+      <c r="D77" s="202"/>
+      <c r="E77" s="202"/>
+      <c r="F77" s="202"/>
+      <c r="G77" s="203"/>
+      <c r="H77" s="135">
+        <f>H74+H76</f>
+        <v>3101073.62</v>
+      </c>
+      <c r="I77" s="130"/>
+      <c r="J77" s="182"/>
+      <c r="K77" s="182"/>
+    </row>
+    <row r="78" spans="1:11" ht="18.75">
+      <c r="A78" s="201" t="s">
         <v>97</v>
       </c>
-      <c r="B75" s="197"/>
-      <c r="C75" s="197"/>
-      <c r="D75" s="197"/>
-      <c r="E75" s="197"/>
-      <c r="F75" s="197"/>
-      <c r="G75" s="198"/>
-      <c r="H75" s="136">
-        <f>H72+H70</f>
-        <v>0</v>
-      </c>
-      <c r="J75" s="146"/>
-    </row>
-    <row r="76" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A76" s="199" t="s">
+      <c r="B78" s="202"/>
+      <c r="C78" s="202"/>
+      <c r="D78" s="202"/>
+      <c r="E78" s="202"/>
+      <c r="F78" s="202"/>
+      <c r="G78" s="203"/>
+      <c r="H78" s="136">
+        <f>H75+H73</f>
+        <v>0</v>
+      </c>
+      <c r="J78" s="146"/>
+    </row>
+    <row r="79" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A79" s="207" t="s">
         <v>87</v>
       </c>
-      <c r="B76" s="200"/>
-      <c r="C76" s="200"/>
-      <c r="D76" s="200"/>
-      <c r="E76" s="200"/>
-      <c r="F76" s="200"/>
-      <c r="G76" s="200"/>
-      <c r="H76" s="137">
-        <f>H73+H70</f>
-        <v>2852037.92</v>
-      </c>
-      <c r="J76" s="7"/>
-    </row>
-    <row r="77" spans="1:11" ht="18.75" hidden="1">
-      <c r="A77" s="217" t="s">
+      <c r="B79" s="208"/>
+      <c r="C79" s="208"/>
+      <c r="D79" s="208"/>
+      <c r="E79" s="208"/>
+      <c r="F79" s="208"/>
+      <c r="G79" s="208"/>
+      <c r="H79" s="137">
+        <f>H76+H73</f>
+        <v>3101073.62</v>
+      </c>
+      <c r="J79" s="7"/>
+    </row>
+    <row r="80" spans="1:11" ht="18.75" hidden="1">
+      <c r="A80" s="194" t="s">
         <v>17</v>
       </c>
-      <c r="B77" s="218"/>
-      <c r="C77" s="218"/>
-      <c r="D77" s="218"/>
-      <c r="E77" s="218"/>
-      <c r="F77" s="218"/>
-      <c r="G77" s="218"/>
-      <c r="H77" s="138">
-        <f>H62</f>
-        <v>0</v>
-      </c>
-      <c r="J77" s="7"/>
-    </row>
-    <row r="78" spans="1:11" ht="18.75" hidden="1">
-      <c r="A78" s="139"/>
-      <c r="B78" s="139"/>
-      <c r="C78" s="139"/>
-      <c r="D78" s="139"/>
-      <c r="E78" s="139"/>
-      <c r="F78" s="139"/>
-      <c r="G78" s="139"/>
-      <c r="H78" s="140"/>
-      <c r="J78" s="7"/>
-    </row>
-    <row r="79" spans="1:11" ht="18.75" hidden="1">
-      <c r="A79" s="139"/>
-      <c r="B79" s="139"/>
-      <c r="C79" s="139"/>
-      <c r="D79" s="139"/>
-      <c r="E79" s="139"/>
-      <c r="F79" s="139"/>
-      <c r="G79" s="139"/>
-      <c r="H79" s="140"/>
-      <c r="J79" s="7"/>
-    </row>
-    <row r="80" spans="1:11" ht="18.75" hidden="1">
-      <c r="A80" s="139"/>
-      <c r="B80" s="139"/>
-      <c r="C80" s="139"/>
-      <c r="D80" s="139"/>
-      <c r="E80" s="139"/>
-      <c r="F80" s="139"/>
-      <c r="G80" s="139"/>
-      <c r="H80" s="140"/>
+      <c r="B80" s="195"/>
+      <c r="C80" s="195"/>
+      <c r="D80" s="195"/>
+      <c r="E80" s="195"/>
+      <c r="F80" s="195"/>
+      <c r="G80" s="195"/>
+      <c r="H80" s="138">
+        <f>H65</f>
+        <v>0</v>
+      </c>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A81" s="141"/>
-      <c r="B81" s="141"/>
-      <c r="C81" s="141"/>
-      <c r="D81" s="141"/>
-      <c r="E81" s="141"/>
-      <c r="F81" s="141"/>
-      <c r="G81" s="141"/>
-      <c r="H81" s="141"/>
-    </row>
-    <row r="82" spans="1:11" ht="18.75">
-      <c r="A82" s="212" t="s">
+    <row r="81" spans="1:11" ht="18.75" hidden="1">
+      <c r="A81" s="139"/>
+      <c r="B81" s="139"/>
+      <c r="C81" s="139"/>
+      <c r="D81" s="139"/>
+      <c r="E81" s="139"/>
+      <c r="F81" s="139"/>
+      <c r="G81" s="139"/>
+      <c r="H81" s="140"/>
+      <c r="J81" s="7"/>
+    </row>
+    <row r="82" spans="1:11" ht="18.75" hidden="1">
+      <c r="A82" s="139"/>
+      <c r="B82" s="139"/>
+      <c r="C82" s="139"/>
+      <c r="D82" s="139"/>
+      <c r="E82" s="139"/>
+      <c r="F82" s="139"/>
+      <c r="G82" s="139"/>
+      <c r="H82" s="140"/>
+      <c r="J82" s="7"/>
+    </row>
+    <row r="83" spans="1:11" ht="18.75" hidden="1">
+      <c r="A83" s="139"/>
+      <c r="B83" s="139"/>
+      <c r="C83" s="139"/>
+      <c r="D83" s="139"/>
+      <c r="E83" s="139"/>
+      <c r="F83" s="139"/>
+      <c r="G83" s="139"/>
+      <c r="H83" s="140"/>
+      <c r="J83" s="7"/>
+    </row>
+    <row r="84" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A84" s="141"/>
+      <c r="B84" s="141"/>
+      <c r="C84" s="141"/>
+      <c r="D84" s="141"/>
+      <c r="E84" s="141"/>
+      <c r="F84" s="141"/>
+      <c r="G84" s="141"/>
+      <c r="H84" s="141"/>
+    </row>
+    <row r="85" spans="1:11" ht="18.75">
+      <c r="A85" s="187" t="s">
         <v>10</v>
       </c>
-      <c r="B82" s="213"/>
-      <c r="C82" s="213"/>
-      <c r="D82" s="213"/>
-      <c r="E82" s="213"/>
-      <c r="F82" s="213"/>
-      <c r="G82" s="213"/>
-      <c r="H82" s="214"/>
-    </row>
-    <row r="83" spans="1:11" ht="18.75">
-      <c r="A83" s="142" t="s">
+      <c r="B85" s="188"/>
+      <c r="C85" s="188"/>
+      <c r="D85" s="188"/>
+      <c r="E85" s="188"/>
+      <c r="F85" s="188"/>
+      <c r="G85" s="188"/>
+      <c r="H85" s="189"/>
+    </row>
+    <row r="86" spans="1:11" ht="18.75">
+      <c r="A86" s="142" t="s">
         <v>12</v>
       </c>
-      <c r="B83" s="143"/>
-      <c r="C83" s="143"/>
-      <c r="D83" s="143"/>
-      <c r="E83" s="143"/>
-      <c r="F83" s="143"/>
-      <c r="G83" s="143"/>
-      <c r="H83" s="144">
-        <v>4908824.1883903649</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
-      <c r="A84" s="82" t="s">
+      <c r="B86" s="143"/>
+      <c r="C86" s="143"/>
+      <c r="D86" s="143"/>
+      <c r="E86" s="143"/>
+      <c r="F86" s="143"/>
+      <c r="G86" s="143"/>
+      <c r="H86" s="144">
+        <v>4403223.2156698657</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="B84" s="83"/>
-      <c r="C84" s="83"/>
-      <c r="D84" s="83"/>
-      <c r="E84" s="83"/>
-      <c r="F84" s="83"/>
-      <c r="G84" s="83"/>
-      <c r="H84" s="145">
+      <c r="B87" s="83"/>
+      <c r="C87" s="83"/>
+      <c r="D87" s="83"/>
+      <c r="E87" s="83"/>
+      <c r="F87" s="83"/>
+      <c r="G87" s="83"/>
+      <c r="H87" s="145">
         <f>Planilla!G32</f>
-        <v>2242499.4201420001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" s="79" t="s">
-        <v>155</v>
-      </c>
-      <c r="B85" s="80"/>
-      <c r="C85" s="80"/>
-      <c r="D85" s="80"/>
-      <c r="E85" s="80"/>
-      <c r="F85" s="80"/>
-      <c r="G85" s="80"/>
-      <c r="H85" s="69">
-        <f>-(H76)</f>
-        <v>-2852037.92</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="B86" s="80"/>
-      <c r="C86" s="80"/>
-      <c r="D86" s="80"/>
-      <c r="E86" s="80"/>
-      <c r="F86" s="80"/>
-      <c r="G86" s="80"/>
-      <c r="H86" s="69">
-        <f>-H63</f>
-        <v>-90000</v>
-      </c>
-      <c r="K86" s="6"/>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="79" t="s">
-        <v>73</v>
-      </c>
-      <c r="B87" s="80" t="s">
-        <v>118</v>
-      </c>
-      <c r="C87" s="80"/>
-      <c r="D87" s="80"/>
-      <c r="E87" s="80"/>
-      <c r="F87" s="80"/>
-      <c r="G87" s="80"/>
-      <c r="H87" s="125">
-        <v>133680</v>
+        <v>2657237.8350200001</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="79" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="B88" s="80"/>
       <c r="C88" s="80"/>
@@ -3336,183 +3354,231 @@
       <c r="E88" s="80"/>
       <c r="F88" s="80"/>
       <c r="G88" s="80"/>
-      <c r="H88" s="125">
-        <v>60257.527137499994</v>
-      </c>
-      <c r="I88" s="146"/>
+      <c r="H88" s="69">
+        <f>-(H79)</f>
+        <v>-3101073.62</v>
+      </c>
     </row>
     <row r="89" spans="1:11">
-      <c r="A89" s="12" t="s">
+      <c r="A89" s="79" t="s">
+        <v>88</v>
+      </c>
+      <c r="B89" s="80"/>
+      <c r="C89" s="80"/>
+      <c r="D89" s="80"/>
+      <c r="E89" s="80"/>
+      <c r="F89" s="80"/>
+      <c r="G89" s="80"/>
+      <c r="H89" s="69">
+        <f>-H66</f>
+        <v>0</v>
+      </c>
+      <c r="K89" s="6"/>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="79" t="s">
+        <v>73</v>
+      </c>
+      <c r="B90" s="80" t="s">
+        <v>118</v>
+      </c>
+      <c r="C90" s="80"/>
+      <c r="D90" s="80"/>
+      <c r="E90" s="80"/>
+      <c r="F90" s="80"/>
+      <c r="G90" s="80"/>
+      <c r="H90" s="125">
+        <v>133680</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="79" t="s">
+        <v>72</v>
+      </c>
+      <c r="B91" s="80"/>
+      <c r="C91" s="80"/>
+      <c r="D91" s="80"/>
+      <c r="E91" s="80"/>
+      <c r="F91" s="80"/>
+      <c r="G91" s="80"/>
+      <c r="H91" s="125">
+        <f>177000-H90</f>
+        <v>43320</v>
+      </c>
+      <c r="I91" s="146"/>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B89" s="84"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="99"/>
-    </row>
-    <row r="90" spans="1:11" ht="18.75">
-      <c r="A90" s="22" t="s">
+      <c r="B92" s="84"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="99"/>
+    </row>
+    <row r="93" spans="1:11" ht="18.75">
+      <c r="A93" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B90" s="23"/>
-      <c r="C90" s="23"/>
-      <c r="D90" s="23"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="23"/>
-      <c r="G90" s="23"/>
-      <c r="H90" s="85">
-        <f>SUM(H83:H89)</f>
-        <v>4403223.2156698657</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="15.75" thickBot="1"/>
-    <row r="92" spans="1:11" ht="16.5" thickBot="1">
-      <c r="A92" s="209" t="s">
+      <c r="B93" s="23"/>
+      <c r="C93" s="23"/>
+      <c r="D93" s="23"/>
+      <c r="E93" s="23"/>
+      <c r="F93" s="23"/>
+      <c r="G93" s="23"/>
+      <c r="H93" s="85">
+        <f>SUM(H86:H92)</f>
+        <v>4136387.4306898657</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="95" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A95" s="184" t="s">
         <v>101</v>
       </c>
-      <c r="B92" s="210"/>
-      <c r="C92" s="210"/>
-      <c r="D92" s="210"/>
-      <c r="E92" s="210"/>
-      <c r="F92" s="210"/>
-      <c r="G92" s="210"/>
-      <c r="H92" s="211"/>
-    </row>
-    <row r="93" spans="1:11" ht="15.75">
-      <c r="A93" s="88" t="s">
+      <c r="B95" s="185"/>
+      <c r="C95" s="185"/>
+      <c r="D95" s="185"/>
+      <c r="E95" s="185"/>
+      <c r="F95" s="185"/>
+      <c r="G95" s="185"/>
+      <c r="H95" s="186"/>
+    </row>
+    <row r="96" spans="1:11" ht="15.75">
+      <c r="A96" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="B93" s="88"/>
-      <c r="C93" s="88"/>
-      <c r="D93" s="88"/>
-      <c r="E93" s="88"/>
-      <c r="F93" s="88"/>
-      <c r="G93" s="88"/>
-      <c r="H93" s="89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="61" t="s">
+      <c r="B96" s="88"/>
+      <c r="C96" s="88"/>
+      <c r="D96" s="88"/>
+      <c r="E96" s="88"/>
+      <c r="F96" s="88"/>
+      <c r="G96" s="88"/>
+      <c r="H96" s="89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="61" t="s">
         <v>125</v>
       </c>
-      <c r="B94" s="92"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="61"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="129"/>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" s="61"/>
-      <c r="B95" s="98"/>
-      <c r="C95" s="61"/>
-      <c r="D95" s="61"/>
-      <c r="E95" s="61"/>
-      <c r="F95" s="61"/>
-      <c r="G95" s="61"/>
-      <c r="H95" s="21"/>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" s="61"/>
-      <c r="B96" s="61"/>
-      <c r="C96" s="61"/>
-      <c r="D96" s="61"/>
-      <c r="E96" s="61"/>
-      <c r="F96" s="61"/>
-      <c r="G96" s="61"/>
-      <c r="H96" s="21"/>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="86" t="s">
+      <c r="B97" s="92"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="61"/>
+      <c r="E97" s="61"/>
+      <c r="F97" s="61"/>
+      <c r="G97" s="61"/>
+      <c r="H97" s="129"/>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="61"/>
+      <c r="B98" s="98"/>
+      <c r="C98" s="61"/>
+      <c r="D98" s="61"/>
+      <c r="E98" s="61"/>
+      <c r="F98" s="61"/>
+      <c r="G98" s="61"/>
+      <c r="H98" s="21"/>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="61"/>
+      <c r="B99" s="61"/>
+      <c r="C99" s="61"/>
+      <c r="D99" s="61"/>
+      <c r="E99" s="61"/>
+      <c r="F99" s="61"/>
+      <c r="G99" s="61"/>
+      <c r="H99" s="21"/>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="B97" s="86"/>
-      <c r="C97" s="86"/>
-      <c r="D97" s="86"/>
-      <c r="E97" s="86"/>
-      <c r="F97" s="86"/>
-      <c r="G97" s="86"/>
-      <c r="H97" s="87">
-        <f>SUM(H93:H96)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" hidden="1">
-      <c r="A100" s="194"/>
-      <c r="B100" s="194"/>
-      <c r="C100" s="194"/>
-      <c r="D100" s="194"/>
-      <c r="E100" s="194"/>
-      <c r="F100" s="194"/>
-      <c r="G100" s="194"/>
-      <c r="H100" s="194"/>
-    </row>
-    <row r="101" spans="1:8" hidden="1">
-      <c r="A101" s="194"/>
-      <c r="B101" s="194"/>
-      <c r="C101" s="194"/>
-      <c r="D101" s="194"/>
-      <c r="E101" s="194"/>
-      <c r="F101" s="194"/>
-      <c r="G101" s="194"/>
-      <c r="H101" s="194"/>
-    </row>
-    <row r="102" spans="1:8" hidden="1">
-      <c r="A102" s="194"/>
-      <c r="B102" s="194"/>
-      <c r="C102" s="194"/>
-      <c r="D102" s="194"/>
-      <c r="E102" s="194"/>
-      <c r="F102" s="194"/>
-      <c r="G102" s="194"/>
-      <c r="H102" s="194"/>
+      <c r="B100" s="86"/>
+      <c r="C100" s="86"/>
+      <c r="D100" s="86"/>
+      <c r="E100" s="86"/>
+      <c r="F100" s="86"/>
+      <c r="G100" s="86"/>
+      <c r="H100" s="87">
+        <f>SUM(H96:H99)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="103" spans="1:8" hidden="1">
-      <c r="A103" s="194"/>
-      <c r="B103" s="194"/>
-      <c r="C103" s="194"/>
-      <c r="D103" s="194"/>
-      <c r="E103" s="194"/>
-      <c r="F103" s="194"/>
-      <c r="G103" s="194"/>
-      <c r="H103" s="194"/>
+      <c r="A103" s="183"/>
+      <c r="B103" s="183"/>
+      <c r="C103" s="183"/>
+      <c r="D103" s="183"/>
+      <c r="E103" s="183"/>
+      <c r="F103" s="183"/>
+      <c r="G103" s="183"/>
+      <c r="H103" s="183"/>
+    </row>
+    <row r="104" spans="1:8" hidden="1">
+      <c r="A104" s="183"/>
+      <c r="B104" s="183"/>
+      <c r="C104" s="183"/>
+      <c r="D104" s="183"/>
+      <c r="E104" s="183"/>
+      <c r="F104" s="183"/>
+      <c r="G104" s="183"/>
+      <c r="H104" s="183"/>
+    </row>
+    <row r="105" spans="1:8" hidden="1">
+      <c r="A105" s="183"/>
+      <c r="B105" s="183"/>
+      <c r="C105" s="183"/>
+      <c r="D105" s="183"/>
+      <c r="E105" s="183"/>
+      <c r="F105" s="183"/>
+      <c r="G105" s="183"/>
+      <c r="H105" s="183"/>
+    </row>
+    <row r="106" spans="1:8" hidden="1">
+      <c r="A106" s="183"/>
+      <c r="B106" s="183"/>
+      <c r="C106" s="183"/>
+      <c r="D106" s="183"/>
+      <c r="E106" s="183"/>
+      <c r="F106" s="183"/>
+      <c r="G106" s="183"/>
+      <c r="H106" s="183"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="A100:H103"/>
-    <mergeCell ref="A92:H92"/>
-    <mergeCell ref="A82:H82"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A67:H68"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="A103:H106"/>
+    <mergeCell ref="A95:H95"/>
+    <mergeCell ref="A85:H85"/>
     <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A80:G80"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A78:G78"/>
     <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A64:H65"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A12:H12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3551,12 +3617,12 @@
       </c>
       <c r="F1" s="106" t="str">
         <f>RESUMEN!F8</f>
-        <v>SEPTIEMBRE</v>
+        <v>OCTUBRE</v>
       </c>
       <c r="G1" s="107"/>
       <c r="H1" s="105" t="str">
         <f>RESUMEN!G8</f>
-        <v>VTO: 15/10</v>
+        <v>VTO: 14/11</v>
       </c>
       <c r="I1" s="104"/>
       <c r="J1" s="104"/>
@@ -3613,10 +3679,7 @@
       <c r="E4" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="124">
-        <f>-107+95200-6</f>
-        <v>95087</v>
-      </c>
+      <c r="F4" s="124"/>
       <c r="G4" s="118"/>
       <c r="H4" s="118"/>
       <c r="I4" s="118"/>
@@ -3630,11 +3693,11 @@
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
       <c r="A5" s="121"/>
-      <c r="B5" s="179">
+      <c r="B5" s="225">
         <f>C3</f>
         <v>3130261.15</v>
       </c>
-      <c r="C5" s="179"/>
+      <c r="C5" s="225"/>
       <c r="D5" s="21"/>
       <c r="E5" s="122">
         <v>70000</v>
@@ -3671,8 +3734,8 @@
     </row>
     <row r="7" spans="1:14" ht="18.75" customHeight="1">
       <c r="A7" s="121"/>
-      <c r="B7" s="179"/>
-      <c r="C7" s="179"/>
+      <c r="B7" s="225"/>
+      <c r="C7" s="225"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="115"/>
@@ -3746,16 +3809,16 @@
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="99">
-        <v>446035.64516714489</v>
-      </c>
-      <c r="G9" s="223"/>
+        <v>593165.56411332928</v>
+      </c>
+      <c r="G9" s="243"/>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
-        <v>446035.64516714489</v>
+        <v>593165.56411332928</v>
       </c>
       <c r="I9" s="68">
         <f>H9*3.7%</f>
-        <v>16503.318871184361</v>
+        <v>21947.125872193188</v>
       </c>
       <c r="J9" s="68">
         <f>IF(G9&gt;F9,G9-F9,0)</f>
@@ -3763,7 +3826,7 @@
       </c>
       <c r="K9" s="68">
         <f>F$4*E9</f>
-        <v>3851.0235000000002</v>
+        <v>0</v>
       </c>
       <c r="L9" s="172">
         <f>B$5*E9</f>
@@ -3775,7 +3838,7 @@
       </c>
       <c r="N9" s="172">
         <f>H9+I9-J9+K9+L9+M9</f>
-        <v>593165.56411332928</v>
+        <v>741888.26656052237</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -3795,7 +3858,7 @@
       <c r="F10" s="17">
         <v>209002.56011999998</v>
       </c>
-      <c r="G10" s="224">
+      <c r="G10" s="241">
         <f>F10</f>
         <v>209002.56011999998</v>
       </c>
@@ -3813,7 +3876,7 @@
       </c>
       <c r="K10" s="24">
         <f t="shared" ref="K10:K31" si="2">F$4*E10</f>
-        <v>6161.6376</v>
+        <v>0</v>
       </c>
       <c r="L10" s="25">
         <f t="shared" ref="L10:L31" si="3">B$5*E10</f>
@@ -3825,7 +3888,7 @@
       </c>
       <c r="N10" s="25">
         <f t="shared" ref="N10:N31" si="5">H10+I10-J10+K10+L10+M10</f>
-        <v>209002.56011999998</v>
+        <v>202840.92251999999</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
@@ -3845,10 +3908,10 @@
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="99">
-        <v>155461.78082999997</v>
-      </c>
-      <c r="G11" s="224">
-        <v>155500</v>
+        <v>155423.56165999995</v>
+      </c>
+      <c r="G11" s="241">
+        <v>155430</v>
       </c>
       <c r="H11" s="68">
         <f t="shared" si="0"/>
@@ -3860,11 +3923,11 @@
       </c>
       <c r="J11" s="68">
         <f t="shared" si="1"/>
-        <v>38.21917000002577</v>
+        <v>6.4383400000515394</v>
       </c>
       <c r="K11" s="68">
         <f t="shared" si="2"/>
-        <v>4583.1934000000001</v>
+        <v>0</v>
       </c>
       <c r="L11" s="172">
         <f t="shared" si="3"/>
@@ -3876,7 +3939,7 @@
       </c>
       <c r="N11" s="172">
         <f>H11+I11-J11+K11+L11+M11+E7</f>
-        <v>155423.56165999995</v>
+        <v>150872.14908999993</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1">
@@ -3896,16 +3959,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F12" s="151">
-        <v>2345245.9687375519</v>
-      </c>
-      <c r="G12" s="225"/>
+        <v>2604576.1956058415</v>
+      </c>
+      <c r="G12" s="231"/>
       <c r="H12" s="152">
         <f t="shared" si="0"/>
-        <v>2345245.9687375519</v>
+        <v>2604576.1956058415</v>
       </c>
       <c r="I12" s="152">
         <f t="shared" si="6"/>
-        <v>86774.10084328943</v>
+        <v>96369.319237416144</v>
       </c>
       <c r="J12" s="152">
         <f t="shared" si="1"/>
@@ -3913,7 +3976,7 @@
       </c>
       <c r="K12" s="152">
         <f t="shared" si="2"/>
-        <v>5087.1544999999996</v>
+        <v>0</v>
       </c>
       <c r="L12" s="153">
         <f t="shared" si="3"/>
@@ -3925,7 +3988,7 @@
       </c>
       <c r="N12" s="153">
         <f t="shared" si="5"/>
-        <v>2604576.1956058415</v>
+        <v>2868414.4863682576</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
@@ -3945,7 +4008,7 @@
       <c r="F13" s="17">
         <v>124175.90377499998</v>
       </c>
-      <c r="G13" s="224">
+      <c r="G13" s="241">
         <f>F13</f>
         <v>124175.90377499998</v>
       </c>
@@ -3963,7 +4026,7 @@
       </c>
       <c r="K13" s="24">
         <f t="shared" si="2"/>
-        <v>3660.8494999999998</v>
+        <v>0</v>
       </c>
       <c r="L13" s="25">
         <f t="shared" si="3"/>
@@ -3975,7 +4038,7 @@
       </c>
       <c r="N13" s="25">
         <f t="shared" si="5"/>
-        <v>124175.90377499998</v>
+        <v>120515.05427499999</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
@@ -3997,7 +4060,7 @@
       <c r="F14" s="17">
         <v>115789.99858500001</v>
       </c>
-      <c r="G14" s="224">
+      <c r="G14" s="241">
         <f>F14</f>
         <v>115789.99858500001</v>
       </c>
@@ -4015,7 +4078,7 @@
       </c>
       <c r="K14" s="24">
         <f t="shared" si="2"/>
-        <v>3413.6233000000002</v>
+        <v>0</v>
       </c>
       <c r="L14" s="25">
         <f t="shared" si="3"/>
@@ -4027,7 +4090,7 @@
       </c>
       <c r="N14" s="25">
         <f t="shared" si="5"/>
-        <v>115789.99858500001</v>
+        <v>112376.375285</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -4047,16 +4110,16 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>133529.41340999998</v>
-      </c>
-      <c r="G15" s="224"/>
+        <v>271999.41511616996</v>
+      </c>
+      <c r="G15" s="241"/>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
-        <v>133529.41340999998</v>
+        <v>271999.41511616996</v>
       </c>
       <c r="I15" s="24">
         <f t="shared" si="6"/>
-        <v>4940.5882961699999</v>
+        <v>10063.978359298289</v>
       </c>
       <c r="J15" s="24">
         <f t="shared" si="1"/>
@@ -4064,7 +4127,7 @@
       </c>
       <c r="K15" s="24">
         <f t="shared" si="2"/>
-        <v>3936.6017999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" s="25">
         <f t="shared" si="3"/>
@@ -4076,7 +4139,7 @@
       </c>
       <c r="N15" s="25">
         <f t="shared" si="5"/>
-        <v>271999.41511616996</v>
+        <v>411656.20508546825</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -4098,7 +4161,7 @@
       <c r="F16" s="17">
         <v>172556.12602500001</v>
       </c>
-      <c r="G16" s="224">
+      <c r="G16" s="241">
         <f>F16</f>
         <v>172556.12602500001</v>
       </c>
@@ -4116,7 +4179,7 @@
       </c>
       <c r="K16" s="24">
         <f t="shared" si="2"/>
-        <v>5087.1544999999996</v>
+        <v>0</v>
       </c>
       <c r="L16" s="25">
         <f t="shared" si="3"/>
@@ -4128,7 +4191,7 @@
       </c>
       <c r="N16" s="25">
         <f t="shared" si="5"/>
-        <v>172556.12602500001</v>
+        <v>167468.971525</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="15" customHeight="1">
@@ -4150,9 +4213,9 @@
       <c r="F17" s="17">
         <v>124175.90377499998</v>
       </c>
-      <c r="G17" s="224">
-        <f>F17</f>
-        <v>124175.90377499998</v>
+      <c r="G17" s="241">
+        <f>F17+24</f>
+        <v>124199.90377499998</v>
       </c>
       <c r="H17" s="24">
         <f t="shared" si="0"/>
@@ -4164,11 +4227,11 @@
       </c>
       <c r="J17" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K17" s="24">
         <f t="shared" si="2"/>
-        <v>3660.8494999999998</v>
+        <v>0</v>
       </c>
       <c r="L17" s="25">
         <f t="shared" si="3"/>
@@ -4180,54 +4243,57 @@
       </c>
       <c r="N17" s="25">
         <f t="shared" si="5"/>
-        <v>124175.90377499998</v>
+        <v>120491.05427499999</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1">
-      <c r="A18" s="147">
+      <c r="A18" s="232">
         <v>10</v>
       </c>
-      <c r="B18" s="154" t="s">
+      <c r="B18" s="233" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="155" t="s">
+      <c r="C18" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="157"/>
-      <c r="E18" s="158">
+      <c r="D18" s="235"/>
+      <c r="E18" s="236">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="F18" s="151">
-        <v>384178.31987136794</v>
-      </c>
-      <c r="G18" s="225"/>
-      <c r="H18" s="152">
+      <c r="F18" s="237">
+        <v>514182.91629160853</v>
+      </c>
+      <c r="G18" s="238">
+        <f>RESUMEN!H51+RESUMEN!H43+RESUMEN!H41</f>
+        <v>177500</v>
+      </c>
+      <c r="H18" s="239">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
-        <v>384178.31987136794</v>
-      </c>
-      <c r="I18" s="152">
+        <v>336682.91629160853</v>
+      </c>
+      <c r="I18" s="239">
         <f t="shared" si="6"/>
-        <v>14214.597835240616</v>
-      </c>
-      <c r="J18" s="152">
+        <v>12457.267902789517</v>
+      </c>
+      <c r="J18" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="152">
+      <c r="K18" s="239">
         <f t="shared" si="2"/>
-        <v>3413.6233000000002</v>
-      </c>
-      <c r="L18" s="153">
+        <v>0</v>
+      </c>
+      <c r="L18" s="240">
         <f t="shared" si="3"/>
         <v>112376.375285</v>
       </c>
-      <c r="M18" s="153">
+      <c r="M18" s="240">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N18" s="153">
+      <c r="N18" s="240">
         <f t="shared" si="5"/>
-        <v>514182.91629160853</v>
+        <v>461516.55947939807</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1">
@@ -4247,16 +4313,16 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F19" s="151">
-        <v>1553193.2961691935</v>
-      </c>
-      <c r="G19" s="225"/>
+        <v>1744190.8615374537</v>
+      </c>
+      <c r="G19" s="231"/>
       <c r="H19" s="152">
         <f t="shared" si="0"/>
-        <v>1553193.2961691935</v>
+        <v>1744190.8615374537</v>
       </c>
       <c r="I19" s="152">
         <f t="shared" si="6"/>
-        <v>57468.151958260169</v>
+        <v>64535.061876885797</v>
       </c>
       <c r="J19" s="152">
         <f t="shared" si="1"/>
@@ -4264,7 +4330,7 @@
       </c>
       <c r="K19" s="152">
         <f t="shared" si="2"/>
-        <v>3936.6017999999999</v>
+        <v>0</v>
       </c>
       <c r="L19" s="153">
         <f t="shared" si="3"/>
@@ -4276,7 +4342,7 @@
       </c>
       <c r="N19" s="153">
         <f t="shared" si="5"/>
-        <v>1744190.8615374537</v>
+        <v>1938318.7350243395</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1">
@@ -4298,9 +4364,9 @@
       <c r="F20" s="17">
         <v>172556.12602500001</v>
       </c>
-      <c r="G20" s="224">
-        <f>F20</f>
-        <v>172556.12602500001</v>
+      <c r="G20" s="241">
+        <f>172600</f>
+        <v>172600</v>
       </c>
       <c r="H20" s="24">
         <f t="shared" si="0"/>
@@ -4312,11 +4378,11 @@
       </c>
       <c r="J20" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>43.873974999994971</v>
       </c>
       <c r="K20" s="24">
         <f t="shared" si="2"/>
-        <v>5087.1544999999996</v>
+        <v>0</v>
       </c>
       <c r="L20" s="25">
         <f t="shared" si="3"/>
@@ -4328,7 +4394,7 @@
       </c>
       <c r="N20" s="25">
         <f t="shared" si="5"/>
-        <v>172556.12602500001</v>
+        <v>167425.09755000001</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1">
@@ -4348,16 +4414,18 @@
         <v>3.85E-2</v>
       </c>
       <c r="F21" s="151">
-        <v>816163.82464434695</v>
-      </c>
-      <c r="G21" s="226"/>
+        <v>970537.78993118776</v>
+      </c>
+      <c r="G21" s="242">
+        <v>241030</v>
+      </c>
       <c r="H21" s="152">
         <f t="shared" si="0"/>
-        <v>816163.82464434695</v>
+        <v>729507.78993118776</v>
       </c>
       <c r="I21" s="152">
         <f t="shared" si="6"/>
-        <v>30198.061511840842</v>
+        <v>26991.788227453952</v>
       </c>
       <c r="J21" s="152">
         <f t="shared" si="1"/>
@@ -4365,7 +4433,7 @@
       </c>
       <c r="K21" s="152">
         <f t="shared" si="2"/>
-        <v>3660.8494999999998</v>
+        <v>0</v>
       </c>
       <c r="L21" s="153">
         <f t="shared" si="3"/>
@@ -4377,7 +4445,7 @@
       </c>
       <c r="N21" s="153">
         <f t="shared" si="5"/>
-        <v>970537.78993118776</v>
+        <v>877014.6324336417</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1">
@@ -4399,7 +4467,7 @@
       <c r="F22" s="17">
         <v>115789.99858500001</v>
       </c>
-      <c r="G22" s="224">
+      <c r="G22" s="241">
         <f>F22</f>
         <v>115789.99858500001</v>
       </c>
@@ -4417,7 +4485,7 @@
       </c>
       <c r="K22" s="24">
         <f t="shared" si="2"/>
-        <v>3413.6233000000002</v>
+        <v>0</v>
       </c>
       <c r="L22" s="25">
         <f t="shared" si="3"/>
@@ -4429,7 +4497,7 @@
       </c>
       <c r="N22" s="25">
         <f t="shared" si="5"/>
-        <v>115789.99858500001</v>
+        <v>112376.375285</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1">
@@ -4451,17 +4519,16 @@
       <c r="F23" s="17">
         <v>133529.41340999998</v>
       </c>
-      <c r="G23" s="224">
-        <f>F23</f>
-        <v>133529.41340999998</v>
+      <c r="G23" s="241">
+        <v>129592</v>
       </c>
       <c r="H23" s="24">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3937.4134099999792</v>
       </c>
       <c r="I23" s="24">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>145.68429616999924</v>
       </c>
       <c r="J23" s="24">
         <f t="shared" si="1"/>
@@ -4469,7 +4536,7 @@
       </c>
       <c r="K23" s="24">
         <f t="shared" si="2"/>
-        <v>3936.6017999999999</v>
+        <v>0</v>
       </c>
       <c r="L23" s="25">
         <f t="shared" si="3"/>
@@ -4481,7 +4548,7 @@
       </c>
       <c r="N23" s="25">
         <f t="shared" si="5"/>
-        <v>133529.41340999998</v>
+        <v>133675.90931616997</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1">
@@ -4501,7 +4568,7 @@
       <c r="F24" s="17">
         <v>172556.12602500001</v>
       </c>
-      <c r="G24" s="224">
+      <c r="G24" s="241">
         <f>F24</f>
         <v>172556.12602500001</v>
       </c>
@@ -4519,7 +4586,7 @@
       </c>
       <c r="K24" s="24">
         <f t="shared" si="2"/>
-        <v>5087.1544999999996</v>
+        <v>0</v>
       </c>
       <c r="L24" s="25">
         <f t="shared" si="3"/>
@@ -4531,7 +4598,7 @@
       </c>
       <c r="N24" s="25">
         <f t="shared" si="5"/>
-        <v>172556.12602500001</v>
+        <v>167468.971525</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="1" customFormat="1" ht="15.75" customHeight="1">
@@ -4553,7 +4620,7 @@
       <c r="F25" s="17">
         <v>124175.90377499998</v>
       </c>
-      <c r="G25" s="224">
+      <c r="G25" s="241">
         <f>F25</f>
         <v>124175.90377499998</v>
       </c>
@@ -4571,7 +4638,7 @@
       </c>
       <c r="K25" s="24">
         <f t="shared" si="2"/>
-        <v>3660.8494999999998</v>
+        <v>0</v>
       </c>
       <c r="L25" s="25">
         <f t="shared" si="3"/>
@@ -4583,7 +4650,7 @@
       </c>
       <c r="N25" s="25">
         <f t="shared" si="5"/>
-        <v>124175.90377499998</v>
+        <v>120515.05427499999</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1">
@@ -4601,11 +4668,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F26" s="17">
-        <v>115646.04427200001</v>
-      </c>
-      <c r="G26" s="224">
+        <v>115789.99858500001</v>
+      </c>
+      <c r="G26" s="241">
         <f>F26</f>
-        <v>115646.04427200001</v>
+        <v>115789.99858500001</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="0"/>
@@ -4621,7 +4688,7 @@
       </c>
       <c r="K26" s="24">
         <f t="shared" si="2"/>
-        <v>3413.6233000000002</v>
+        <v>0</v>
       </c>
       <c r="L26" s="25">
         <f t="shared" si="3"/>
@@ -4633,7 +4700,7 @@
       </c>
       <c r="N26" s="25">
         <f t="shared" si="5"/>
-        <v>115789.99858500001</v>
+        <v>112376.375285</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1">
@@ -4653,18 +4720,18 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F27" s="151">
-        <v>2597093.1214901991</v>
-      </c>
-      <c r="G27" s="225">
-        <v>133550</v>
+        <v>2688223.6303953365</v>
+      </c>
+      <c r="G27" s="231">
+        <v>133530</v>
       </c>
       <c r="H27" s="174">
         <f t="shared" si="0"/>
-        <v>2463543.1214901991</v>
+        <v>2554693.6303953365</v>
       </c>
       <c r="I27" s="152">
         <f t="shared" si="6"/>
-        <v>91151.095495137386</v>
+        <v>94523.664324627462</v>
       </c>
       <c r="J27" s="152">
         <f t="shared" si="1"/>
@@ -4672,7 +4739,7 @@
       </c>
       <c r="K27" s="152">
         <f t="shared" si="2"/>
-        <v>3936.6017999999999</v>
+        <v>0</v>
       </c>
       <c r="L27" s="153">
         <f t="shared" si="3"/>
@@ -4684,7 +4751,7 @@
       </c>
       <c r="N27" s="153">
         <f t="shared" si="5"/>
-        <v>2688223.6303953365</v>
+        <v>2778810.106329964</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="17.25" customHeight="1">
@@ -4702,16 +4769,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>591912.45477272919</v>
-      </c>
-      <c r="G28" s="224"/>
+        <v>781282.18712432007</v>
+      </c>
+      <c r="G28" s="241"/>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
-        <v>591912.45477272919</v>
+        <v>781282.18712432007</v>
       </c>
       <c r="I28" s="24">
         <f t="shared" si="6"/>
-        <v>21900.760826590984</v>
+        <v>28907.440923599846</v>
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
@@ -4728,7 +4795,7 @@
       </c>
       <c r="N28" s="25">
         <f t="shared" si="5"/>
-        <v>781282.18712432007</v>
+        <v>977658.59957292001</v>
       </c>
       <c r="O28" s="7"/>
     </row>
@@ -4749,9 +4816,9 @@
       <c r="F29" s="17">
         <v>124175.90377499998</v>
       </c>
-      <c r="G29" s="224">
-        <f>F29</f>
-        <v>124175.90377499998</v>
+      <c r="G29" s="241">
+        <f>F29+24</f>
+        <v>124199.90377499998</v>
       </c>
       <c r="H29" s="24">
         <f t="shared" si="0"/>
@@ -4763,11 +4830,11 @@
       </c>
       <c r="J29" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K29" s="24">
         <f t="shared" si="2"/>
-        <v>3660.8494999999998</v>
+        <v>0</v>
       </c>
       <c r="L29" s="25">
         <f t="shared" si="3"/>
@@ -4779,7 +4846,7 @@
       </c>
       <c r="N29" s="25">
         <f t="shared" si="5"/>
-        <v>124175.90377499998</v>
+        <v>120491.05427499999</v>
       </c>
       <c r="O29" s="7"/>
     </row>
@@ -4802,7 +4869,7 @@
       <c r="F30" s="17">
         <v>115789.99858500001</v>
       </c>
-      <c r="G30" s="224">
+      <c r="G30" s="241">
         <f>F30</f>
         <v>115789.99858500001</v>
       </c>
@@ -4820,7 +4887,7 @@
       </c>
       <c r="K30" s="24">
         <f t="shared" si="2"/>
-        <v>3413.6233000000002</v>
+        <v>0</v>
       </c>
       <c r="L30" s="25">
         <f t="shared" si="3"/>
@@ -4832,7 +4899,7 @@
       </c>
       <c r="N30" s="25">
         <f t="shared" si="5"/>
-        <v>115789.99858500001</v>
+        <v>112376.375285</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15" customHeight="1">
@@ -4852,7 +4919,7 @@
       <c r="F31" s="17">
         <v>133529.41340999998</v>
       </c>
-      <c r="G31" s="224">
+      <c r="G31" s="241">
         <f>F31</f>
         <v>133529.41340999998</v>
       </c>
@@ -4870,7 +4937,7 @@
       </c>
       <c r="K31" s="24">
         <f t="shared" si="2"/>
-        <v>3936.6017999999999</v>
+        <v>0</v>
       </c>
       <c r="L31" s="25">
         <f t="shared" si="3"/>
@@ -4882,7 +4949,7 @@
       </c>
       <c r="N31" s="25">
         <f t="shared" si="5"/>
-        <v>133529.41340999998</v>
+        <v>129592.81160999999</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15.75">
@@ -4899,27 +4966,27 @@
       </c>
       <c r="F32" s="100">
         <f>SUM(F9:F31)</f>
-        <v>10976263.245234534</v>
+        <v>12277175.496230245</v>
       </c>
       <c r="G32" s="100">
         <f>SUM(G9:G31)</f>
-        <v>2242499.4201420001</v>
+        <v>2657237.8350200001</v>
       </c>
       <c r="H32" s="126">
         <f>SUM(H9:H31)</f>
-        <v>8733802.0442625321</v>
+        <v>9620035.9735252466</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>323150.67563771381</v>
+        <v>355941.33102043415</v>
       </c>
       <c r="J32" s="100">
         <f t="shared" ref="J32" si="7">SUM(J9:J31)</f>
-        <v>38.21917000002577</v>
+        <v>98.31231500004651</v>
       </c>
       <c r="K32" s="91">
         <f>SUM(K9:K31)</f>
-        <v>89999.845499999996</v>
+        <v>0</v>
       </c>
       <c r="L32" s="54">
         <f>SUM(L9:L31)</f>
@@ -4931,117 +4998,117 @@
       </c>
       <c r="N32" s="54">
         <f>SUM(N9:N31)</f>
-        <v>12277175.496230245</v>
+        <v>13106140.14223068</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:14" hidden="1">
-      <c r="B34" s="178"/>
-      <c r="C34" s="178"/>
-      <c r="D34" s="178"/>
-      <c r="E34" s="178"/>
-      <c r="F34" s="178"/>
-      <c r="G34" s="178"/>
-      <c r="H34" s="178"/>
-      <c r="I34" s="178"/>
-      <c r="J34" s="178"/>
-      <c r="K34" s="178"/>
-      <c r="L34" s="178"/>
-      <c r="M34" s="178"/>
-      <c r="N34" s="178"/>
+      <c r="B34" s="224"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
+      <c r="F34" s="224"/>
+      <c r="G34" s="224"/>
+      <c r="H34" s="224"/>
+      <c r="I34" s="224"/>
+      <c r="J34" s="224"/>
+      <c r="K34" s="224"/>
+      <c r="L34" s="224"/>
+      <c r="M34" s="224"/>
+      <c r="N34" s="224"/>
     </row>
     <row r="35" spans="1:14" hidden="1">
-      <c r="B35" s="178"/>
-      <c r="C35" s="178"/>
-      <c r="D35" s="178"/>
-      <c r="E35" s="178"/>
-      <c r="F35" s="178"/>
-      <c r="G35" s="178"/>
-      <c r="H35" s="178"/>
-      <c r="I35" s="178"/>
-      <c r="J35" s="178"/>
-      <c r="K35" s="178"/>
-      <c r="L35" s="178"/>
-      <c r="M35" s="178"/>
-      <c r="N35" s="178"/>
+      <c r="B35" s="224"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
+      <c r="H35" s="224"/>
+      <c r="I35" s="224"/>
+      <c r="J35" s="224"/>
+      <c r="K35" s="224"/>
+      <c r="L35" s="224"/>
+      <c r="M35" s="224"/>
+      <c r="N35" s="224"/>
     </row>
     <row r="36" spans="1:14" hidden="1">
-      <c r="B36" s="178"/>
-      <c r="C36" s="178"/>
-      <c r="D36" s="178"/>
-      <c r="E36" s="178"/>
-      <c r="F36" s="178"/>
-      <c r="G36" s="178"/>
-      <c r="H36" s="178"/>
-      <c r="I36" s="178"/>
-      <c r="J36" s="178"/>
-      <c r="K36" s="178"/>
-      <c r="L36" s="178"/>
-      <c r="M36" s="178"/>
-      <c r="N36" s="178"/>
+      <c r="B36" s="224"/>
+      <c r="C36" s="224"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="224"/>
+      <c r="F36" s="224"/>
+      <c r="G36" s="224"/>
+      <c r="H36" s="224"/>
+      <c r="I36" s="224"/>
+      <c r="J36" s="224"/>
+      <c r="K36" s="224"/>
+      <c r="L36" s="224"/>
+      <c r="M36" s="224"/>
+      <c r="N36" s="224"/>
     </row>
     <row r="37" spans="1:14" hidden="1">
-      <c r="B37" s="178"/>
-      <c r="C37" s="178"/>
-      <c r="D37" s="178"/>
-      <c r="E37" s="178"/>
-      <c r="F37" s="178"/>
-      <c r="G37" s="178"/>
-      <c r="H37" s="178"/>
-      <c r="I37" s="178"/>
-      <c r="J37" s="178"/>
-      <c r="K37" s="178"/>
-      <c r="L37" s="178"/>
-      <c r="M37" s="178"/>
-      <c r="N37" s="178"/>
+      <c r="B37" s="224"/>
+      <c r="C37" s="224"/>
+      <c r="D37" s="224"/>
+      <c r="E37" s="224"/>
+      <c r="F37" s="224"/>
+      <c r="G37" s="224"/>
+      <c r="H37" s="224"/>
+      <c r="I37" s="224"/>
+      <c r="J37" s="224"/>
+      <c r="K37" s="224"/>
+      <c r="L37" s="224"/>
+      <c r="M37" s="224"/>
+      <c r="N37" s="224"/>
     </row>
     <row r="38" spans="1:14" hidden="1">
-      <c r="A38" s="180"/>
-      <c r="B38" s="180"/>
-      <c r="C38" s="180"/>
-      <c r="D38" s="180"/>
-      <c r="E38" s="180"/>
-      <c r="F38" s="180"/>
-      <c r="G38" s="180"/>
-      <c r="H38" s="180"/>
-      <c r="I38" s="180"/>
-      <c r="J38" s="180"/>
-      <c r="K38" s="180"/>
-      <c r="L38" s="180"/>
-      <c r="M38" s="180"/>
-      <c r="N38" s="180"/>
+      <c r="A38" s="226"/>
+      <c r="B38" s="226"/>
+      <c r="C38" s="226"/>
+      <c r="D38" s="226"/>
+      <c r="E38" s="226"/>
+      <c r="F38" s="226"/>
+      <c r="G38" s="226"/>
+      <c r="H38" s="226"/>
+      <c r="I38" s="226"/>
+      <c r="J38" s="226"/>
+      <c r="K38" s="226"/>
+      <c r="L38" s="226"/>
+      <c r="M38" s="226"/>
+      <c r="N38" s="226"/>
     </row>
     <row r="39" spans="1:14" hidden="1">
-      <c r="A39" s="180"/>
-      <c r="B39" s="180"/>
-      <c r="C39" s="180"/>
-      <c r="D39" s="180"/>
-      <c r="E39" s="180"/>
-      <c r="F39" s="180"/>
-      <c r="G39" s="180"/>
-      <c r="H39" s="180"/>
-      <c r="I39" s="180"/>
-      <c r="J39" s="180"/>
-      <c r="K39" s="180"/>
-      <c r="L39" s="180"/>
-      <c r="M39" s="180"/>
-      <c r="N39" s="180"/>
+      <c r="A39" s="226"/>
+      <c r="B39" s="226"/>
+      <c r="C39" s="226"/>
+      <c r="D39" s="226"/>
+      <c r="E39" s="226"/>
+      <c r="F39" s="226"/>
+      <c r="G39" s="226"/>
+      <c r="H39" s="226"/>
+      <c r="I39" s="226"/>
+      <c r="J39" s="226"/>
+      <c r="K39" s="226"/>
+      <c r="L39" s="226"/>
+      <c r="M39" s="226"/>
+      <c r="N39" s="226"/>
     </row>
     <row r="40" spans="1:14" hidden="1">
-      <c r="A40" s="180"/>
-      <c r="B40" s="180"/>
-      <c r="C40" s="180"/>
-      <c r="D40" s="180"/>
-      <c r="E40" s="180"/>
-      <c r="F40" s="180"/>
-      <c r="G40" s="180"/>
-      <c r="H40" s="180"/>
-      <c r="I40" s="180"/>
-      <c r="J40" s="180"/>
-      <c r="K40" s="180"/>
-      <c r="L40" s="180"/>
-      <c r="M40" s="180"/>
-      <c r="N40" s="180"/>
+      <c r="A40" s="226"/>
+      <c r="B40" s="226"/>
+      <c r="C40" s="226"/>
+      <c r="D40" s="226"/>
+      <c r="E40" s="226"/>
+      <c r="F40" s="226"/>
+      <c r="G40" s="226"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="226"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="226"/>
+      <c r="M40" s="226"/>
+      <c r="N40" s="226"/>
     </row>
     <row r="41" spans="1:14">
       <c r="N41" s="7"/>
@@ -5072,15 +5139,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="181" t="s">
+      <c r="A1" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="183"/>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
+      <c r="G1" s="229"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>

--- a/BRIN 3219/Octubre/BRIN3219-EXPENSAS-Octubre.xlsx
+++ b/BRIN 3219/Octubre/BRIN3219-EXPENSAS-Octubre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BRIN 3219\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C17160-758B-48A0-95E0-73FE9D94A23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D19B1A-2721-424E-9EC8-C3151C436238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$N$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$102</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="162">
   <si>
     <t>U.F.</t>
   </si>
@@ -274,9 +274,6 @@
   </si>
   <si>
     <t>ORDINARIOS:</t>
-  </si>
-  <si>
-    <t>EXTRAORDINARIOS:</t>
   </si>
   <si>
     <t>SUTHER / FATHERY</t>
@@ -477,9 +474,6 @@
     <t>INTERES por MORA 3,7%</t>
   </si>
   <si>
-    <t>GASTOS EXTR. ASCENSOR Y LIBROS</t>
-  </si>
-  <si>
     <t>Horas extra fumigacion</t>
   </si>
   <si>
@@ -498,9 +492,6 @@
     <t>AYSA</t>
   </si>
   <si>
-    <t>VTO: 14/11</t>
-  </si>
-  <si>
     <t>OCTUBRE</t>
   </si>
   <si>
@@ -516,7 +507,28 @@
     <t>Destapacion AYSA - 31/10</t>
   </si>
   <si>
-    <t>Julio Doartero - Arreglo cisterna - 30/10</t>
+    <t xml:space="preserve">Romera Carlos Augusto </t>
+  </si>
+  <si>
+    <t>Abono juicio - UF 5.20</t>
+  </si>
+  <si>
+    <t>Dr. Sarro Murillo escrito</t>
+  </si>
+  <si>
+    <t>Adelanto arreglo ascensor</t>
+  </si>
+  <si>
+    <t>Julio Doartero - Destrabe cisterna - 30/10</t>
+  </si>
+  <si>
+    <t>Pago Juicio cuota 1/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pago Juicio </t>
+  </si>
+  <si>
+    <t>VTO: 30/11</t>
   </si>
 </sst>
 </file>
@@ -1443,7 +1455,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1622,152 +1633,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="30" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1778,12 +1643,159 @@
     <xf numFmtId="0" fontId="25" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="30" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="30" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2230,7 +2242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -2255,23 +2267,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="215"/>
-      <c r="G2" s="215"/>
-      <c r="H2" s="216"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="190"/>
+      <c r="F2" s="190"/>
+      <c r="G2" s="190"/>
+      <c r="H2" s="191"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="190">
+      <c r="E3" s="223">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="191"/>
+      <c r="F3" s="223"/>
+      <c r="G3" s="223"/>
+      <c r="H3" s="224"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2299,7 +2311,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H6" s="11"/>
     </row>
@@ -2317,11 +2329,11 @@
       <c r="E8" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="90" t="s">
-        <v>152</v>
+      <c r="F8" s="89" t="s">
+        <v>149</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -2350,14 +2362,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="222"/>
-      <c r="B12" s="183"/>
-      <c r="C12" s="183"/>
-      <c r="D12" s="183"/>
-      <c r="E12" s="183"/>
-      <c r="F12" s="183"/>
-      <c r="G12" s="183"/>
-      <c r="H12" s="223"/>
+      <c r="A12" s="201"/>
+      <c r="B12" s="202"/>
+      <c r="C12" s="202"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="202"/>
+      <c r="G12" s="202"/>
+      <c r="H12" s="203"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2370,695 +2382,703 @@
       <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:9" ht="15.75">
-      <c r="A14" s="196" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="196"/>
-      <c r="C14" s="196"/>
-      <c r="D14" s="196"/>
-      <c r="E14" s="196"/>
-      <c r="F14" s="196"/>
-      <c r="G14" s="196"/>
-      <c r="H14" s="196"/>
+      <c r="A14" s="227" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="227"/>
+      <c r="C14" s="227"/>
+      <c r="D14" s="227"/>
+      <c r="E14" s="227"/>
+      <c r="F14" s="227"/>
+      <c r="G14" s="227"/>
+      <c r="H14" s="227"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="178" t="s">
-        <v>149</v>
-      </c>
-      <c r="B15" s="141"/>
-      <c r="C15" s="141"/>
-      <c r="D15" s="141"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="141"/>
-      <c r="G15" s="141"/>
-      <c r="H15" s="230">
+      <c r="A15" s="177" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="140"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="140"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="140"/>
+      <c r="G15" s="140"/>
+      <c r="H15" s="73">
         <v>381604.3</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="178" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="141"/>
-      <c r="C16" s="141"/>
-      <c r="D16" s="141"/>
-      <c r="E16" s="141"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="141"/>
-      <c r="H16" s="230">
+      <c r="A16" s="177" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="140"/>
+      <c r="C16" s="140"/>
+      <c r="D16" s="140"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="140"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="73">
         <v>-60102.67</v>
       </c>
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="178" t="s">
-        <v>122</v>
-      </c>
-      <c r="B17" s="141"/>
-      <c r="C17" s="141"/>
-      <c r="D17" s="141"/>
-      <c r="E17" s="141"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="141"/>
-      <c r="H17" s="230">
+      <c r="A17" s="177" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" s="140"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="140"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="140"/>
+      <c r="G17" s="140"/>
+      <c r="H17" s="73">
         <v>0.37</v>
       </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="178" t="s">
+      <c r="A18" s="177" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="141"/>
-      <c r="C18" s="141"/>
-      <c r="D18" s="141"/>
-      <c r="E18" s="141"/>
-      <c r="F18" s="141"/>
-      <c r="G18" s="141"/>
-      <c r="H18" s="70">
+      <c r="B18" s="140"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="140"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="140"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="69">
         <f>SUM(H15:H17)</f>
         <v>321502</v>
       </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" ht="0.75" customHeight="1">
-      <c r="A19" s="218" t="s">
+      <c r="A19" s="197" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" s="197"/>
+      <c r="C19" s="197"/>
+      <c r="D19" s="197"/>
+      <c r="E19" s="197"/>
+      <c r="F19" s="197"/>
+      <c r="G19" s="197"/>
+      <c r="H19" s="197"/>
+    </row>
+    <row r="20" spans="1:9" hidden="1">
+      <c r="A20" s="177" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="140"/>
+      <c r="C20" s="140"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="140"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="73"/>
+    </row>
+    <row r="21" spans="1:9" hidden="1">
+      <c r="A21" s="177"/>
+      <c r="B21" s="140"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="140"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" hidden="1">
+      <c r="A22" s="177"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
+      <c r="D22" s="140"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="140"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" hidden="1">
+      <c r="A23" s="177"/>
+      <c r="B23" s="140"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="140"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="140"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" hidden="1">
+      <c r="A24" s="177" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="218"/>
-      <c r="C19" s="218"/>
-      <c r="D19" s="218"/>
-      <c r="E19" s="218"/>
-      <c r="F19" s="218"/>
-      <c r="G19" s="218"/>
-      <c r="H19" s="218"/>
-    </row>
-    <row r="20" spans="1:9" hidden="1">
-      <c r="A20" s="178" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="141"/>
-      <c r="C20" s="141"/>
-      <c r="D20" s="141"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="74"/>
-    </row>
-    <row r="21" spans="1:9" hidden="1">
-      <c r="A21" s="178"/>
-      <c r="B21" s="141"/>
-      <c r="C21" s="141"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="141"/>
-      <c r="G21" s="141"/>
-      <c r="H21" s="74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" hidden="1">
-      <c r="A22" s="178"/>
-      <c r="B22" s="141"/>
-      <c r="C22" s="141"/>
-      <c r="D22" s="141"/>
-      <c r="E22" s="141"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="141"/>
-      <c r="H22" s="74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" hidden="1">
-      <c r="A23" s="178"/>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
-      <c r="D23" s="141"/>
-      <c r="E23" s="141"/>
-      <c r="F23" s="141"/>
-      <c r="G23" s="141"/>
-      <c r="H23" s="74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" hidden="1">
-      <c r="A24" s="178" t="s">
-        <v>133</v>
-      </c>
-      <c r="B24" s="141"/>
-      <c r="C24" s="141"/>
-      <c r="D24" s="141"/>
-      <c r="E24" s="141"/>
-      <c r="F24" s="141"/>
-      <c r="G24" s="141"/>
-      <c r="H24" s="74"/>
+      <c r="B24" s="140"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="140"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="140"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="73"/>
     </row>
     <row r="25" spans="1:9" hidden="1">
-      <c r="A25" s="178" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="141"/>
-      <c r="C25" s="141"/>
-      <c r="D25" s="141"/>
-      <c r="E25" s="141"/>
-      <c r="F25" s="141"/>
-      <c r="G25" s="141"/>
-      <c r="H25" s="74"/>
+      <c r="A25" s="177" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="140"/>
+      <c r="C25" s="140"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="73"/>
     </row>
     <row r="26" spans="1:9" hidden="1">
-      <c r="A26" s="178" t="s">
+      <c r="A26" s="177" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="141"/>
-      <c r="C26" s="141"/>
-      <c r="D26" s="141"/>
-      <c r="E26" s="141"/>
-      <c r="F26" s="141"/>
-      <c r="G26" s="141"/>
-      <c r="H26" s="70">
+      <c r="B26" s="140"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="69">
         <f>SUM(H20:H25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="217" t="s">
-        <v>136</v>
-      </c>
-      <c r="B27" s="217"/>
-      <c r="C27" s="217"/>
-      <c r="D27" s="217"/>
-      <c r="E27" s="217"/>
-      <c r="F27" s="217"/>
-      <c r="G27" s="217"/>
-      <c r="H27" s="217"/>
+      <c r="A27" s="196" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="196"/>
+      <c r="C27" s="196"/>
+      <c r="D27" s="196"/>
+      <c r="E27" s="196"/>
+      <c r="F27" s="196"/>
+      <c r="G27" s="196"/>
+      <c r="H27" s="196"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="141" t="s">
-        <v>145</v>
-      </c>
-      <c r="B28" s="141"/>
-      <c r="C28" s="141"/>
-      <c r="D28" s="141"/>
-      <c r="E28" s="141"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="141"/>
-      <c r="H28" s="230">
+      <c r="A28" s="140" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="140"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="140"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="73">
         <v>32000</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="141"/>
-      <c r="B29" s="141"/>
-      <c r="C29" s="141"/>
-      <c r="D29" s="141"/>
-      <c r="E29" s="141"/>
-      <c r="F29" s="141"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="74"/>
+      <c r="A29" s="140"/>
+      <c r="B29" s="140"/>
+      <c r="C29" s="140"/>
+      <c r="D29" s="140"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="73"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="141" t="s">
+      <c r="A30" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="141"/>
-      <c r="C30" s="141"/>
-      <c r="D30" s="141"/>
-      <c r="E30" s="141"/>
-      <c r="F30" s="141"/>
-      <c r="G30" s="141"/>
-      <c r="H30" s="70">
+      <c r="B30" s="140"/>
+      <c r="C30" s="140"/>
+      <c r="D30" s="140"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="140"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="69">
         <f>SUM(H28:H29)</f>
         <v>32000</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A31" s="197" t="s">
-        <v>90</v>
-      </c>
-      <c r="B31" s="197"/>
-      <c r="C31" s="197"/>
-      <c r="D31" s="197"/>
-      <c r="E31" s="197"/>
-      <c r="F31" s="197"/>
-      <c r="G31" s="197"/>
-      <c r="H31" s="197"/>
+      <c r="A31" s="192" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" s="192"/>
+      <c r="C31" s="192"/>
+      <c r="D31" s="192"/>
+      <c r="E31" s="192"/>
+      <c r="F31" s="192"/>
+      <c r="G31" s="192"/>
+      <c r="H31" s="192"/>
     </row>
     <row r="32" spans="1:9" hidden="1">
-      <c r="A32" s="178"/>
-      <c r="B32" s="141"/>
-      <c r="C32" s="141"/>
-      <c r="D32" s="141"/>
-      <c r="E32" s="141"/>
-      <c r="F32" s="141"/>
-      <c r="G32" s="141"/>
-      <c r="H32" s="74"/>
+      <c r="A32" s="177"/>
+      <c r="B32" s="140"/>
+      <c r="C32" s="140"/>
+      <c r="D32" s="140"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="140"/>
+      <c r="G32" s="140"/>
+      <c r="H32" s="73"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="178" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="179"/>
-      <c r="C33" s="141"/>
-      <c r="D33" s="141"/>
-      <c r="E33" s="141"/>
-      <c r="F33" s="141"/>
-      <c r="G33" s="141"/>
-      <c r="H33" s="230">
+      <c r="A33" s="177" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="178"/>
+      <c r="C33" s="140"/>
+      <c r="D33" s="140"/>
+      <c r="E33" s="140"/>
+      <c r="F33" s="140"/>
+      <c r="G33" s="140"/>
+      <c r="H33" s="73">
         <f>1623.15+33810.99+14068.38</f>
         <v>49502.52</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="141" t="s">
-        <v>146</v>
-      </c>
-      <c r="B34" s="141"/>
-      <c r="C34" s="141"/>
-      <c r="D34" s="141"/>
-      <c r="E34" s="141"/>
-      <c r="F34" s="141"/>
-      <c r="G34" s="141"/>
-      <c r="H34" s="74">
+      <c r="A34" s="140" t="s">
+        <v>144</v>
+      </c>
+      <c r="B34" s="140"/>
+      <c r="C34" s="140"/>
+      <c r="D34" s="140"/>
+      <c r="E34" s="140"/>
+      <c r="F34" s="140"/>
+      <c r="G34" s="140"/>
+      <c r="H34" s="73">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="141" t="s">
+      <c r="A35" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="141"/>
-      <c r="C35" s="141"/>
-      <c r="D35" s="141"/>
-      <c r="E35" s="141"/>
-      <c r="F35" s="141"/>
-      <c r="G35" s="141"/>
-      <c r="H35" s="70">
+      <c r="B35" s="140"/>
+      <c r="C35" s="140"/>
+      <c r="D35" s="140"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="140"/>
+      <c r="G35" s="140"/>
+      <c r="H35" s="69">
         <f>SUM(H32:H34)</f>
         <v>49502.52</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="197" t="s">
-        <v>137</v>
-      </c>
-      <c r="B36" s="197"/>
-      <c r="C36" s="197"/>
-      <c r="D36" s="197"/>
-      <c r="E36" s="197"/>
-      <c r="F36" s="197"/>
-      <c r="G36" s="197"/>
-      <c r="H36" s="197"/>
+      <c r="A36" s="192" t="s">
+        <v>136</v>
+      </c>
+      <c r="B36" s="192"/>
+      <c r="C36" s="192"/>
+      <c r="D36" s="192"/>
+      <c r="E36" s="192"/>
+      <c r="F36" s="192"/>
+      <c r="G36" s="192"/>
+      <c r="H36" s="192"/>
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A37" s="141" t="s">
-        <v>150</v>
-      </c>
-      <c r="B37" s="141"/>
-      <c r="C37" s="141"/>
-      <c r="D37" s="141"/>
-      <c r="E37" s="141"/>
-      <c r="F37" s="141"/>
-      <c r="G37" s="141"/>
-      <c r="H37" s="230">
+      <c r="A37" s="140" t="s">
+        <v>148</v>
+      </c>
+      <c r="B37" s="140"/>
+      <c r="C37" s="140"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140"/>
+      <c r="H37" s="73">
         <v>2056747.63</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="180" t="s">
-        <v>102</v>
-      </c>
-      <c r="B38" s="141"/>
-      <c r="C38" s="141"/>
-      <c r="D38" s="141"/>
-      <c r="E38" s="141"/>
-      <c r="F38" s="141"/>
-      <c r="G38" s="141"/>
-      <c r="H38" s="230">
+      <c r="A38" s="179" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="140"/>
+      <c r="C38" s="140"/>
+      <c r="D38" s="140"/>
+      <c r="E38" s="140"/>
+      <c r="F38" s="140"/>
+      <c r="G38" s="140"/>
+      <c r="H38" s="73">
         <v>56106.559999999998</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="141" t="s">
+      <c r="A39" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="141"/>
-      <c r="C39" s="141"/>
-      <c r="D39" s="141"/>
-      <c r="E39" s="141"/>
-      <c r="F39" s="141"/>
-      <c r="G39" s="141"/>
-      <c r="H39" s="181">
+      <c r="B39" s="140"/>
+      <c r="C39" s="140"/>
+      <c r="D39" s="140"/>
+      <c r="E39" s="140"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="180">
         <f>SUM(H37:H38)</f>
         <v>2112854.19</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="196" t="s">
-        <v>138</v>
-      </c>
-      <c r="B40" s="196"/>
-      <c r="C40" s="196"/>
-      <c r="D40" s="196"/>
-      <c r="E40" s="196"/>
-      <c r="F40" s="196"/>
-      <c r="G40" s="196"/>
-      <c r="H40" s="196"/>
+      <c r="A40" s="227" t="s">
+        <v>137</v>
+      </c>
+      <c r="B40" s="227"/>
+      <c r="C40" s="227"/>
+      <c r="D40" s="227"/>
+      <c r="E40" s="227"/>
+      <c r="F40" s="227"/>
+      <c r="G40" s="227"/>
+      <c r="H40" s="227"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="81" t="s">
+      <c r="A41" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="141"/>
-      <c r="C41" s="141"/>
-      <c r="D41" s="141"/>
-      <c r="E41" s="141"/>
-      <c r="F41" s="141"/>
-      <c r="G41" s="141"/>
-      <c r="H41" s="230">
+      <c r="B41" s="140"/>
+      <c r="C41" s="140"/>
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="140"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="73">
         <v>77500</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="141" t="s">
+      <c r="A42" s="140" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="141"/>
-      <c r="C42" s="141"/>
-      <c r="D42" s="141"/>
-      <c r="E42" s="141"/>
-      <c r="F42" s="141"/>
-      <c r="G42" s="141"/>
-      <c r="H42" s="230">
+      <c r="B42" s="140"/>
+      <c r="C42" s="140"/>
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="73">
         <v>20774.91</v>
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="141" t="s">
+      <c r="A43" s="140" t="s">
+        <v>150</v>
+      </c>
+      <c r="B43" s="140"/>
+      <c r="C43" s="140"/>
+      <c r="D43" s="140"/>
+      <c r="E43" s="140"/>
+      <c r="F43" s="140"/>
+      <c r="G43" s="140"/>
+      <c r="H43" s="73">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="140" t="s">
         <v>153</v>
       </c>
-      <c r="B43" s="141"/>
-      <c r="C43" s="141"/>
-      <c r="D43" s="141"/>
-      <c r="E43" s="141"/>
-      <c r="F43" s="141"/>
-      <c r="G43" s="141"/>
-      <c r="H43" s="230">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="141" t="s">
-        <v>156</v>
-      </c>
-      <c r="B44" s="141"/>
-      <c r="C44" s="141"/>
-      <c r="D44" s="141"/>
-      <c r="E44" s="141"/>
-      <c r="F44" s="141"/>
-      <c r="G44" s="141"/>
-      <c r="H44" s="230">
+      <c r="B44" s="140"/>
+      <c r="C44" s="140"/>
+      <c r="D44" s="140"/>
+      <c r="E44" s="140"/>
+      <c r="F44" s="140"/>
+      <c r="G44" s="140"/>
+      <c r="H44" s="73">
         <v>50000</v>
       </c>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="141" t="s">
-        <v>157</v>
-      </c>
-      <c r="B45" s="141"/>
-      <c r="C45" s="141"/>
-      <c r="D45" s="141"/>
-      <c r="E45" s="141"/>
-      <c r="F45" s="141"/>
-      <c r="G45" s="141"/>
-      <c r="H45" s="230">
+      <c r="A45" s="140" t="s">
+        <v>158</v>
+      </c>
+      <c r="B45" s="140"/>
+      <c r="C45" s="140"/>
+      <c r="D45" s="140"/>
+      <c r="E45" s="140"/>
+      <c r="F45" s="140"/>
+      <c r="G45" s="140"/>
+      <c r="H45" s="73">
         <v>60000</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A46" s="141" t="s">
-        <v>155</v>
-      </c>
-      <c r="B46" s="141"/>
-      <c r="C46" s="141"/>
-      <c r="D46" s="141"/>
-      <c r="E46" s="141"/>
-      <c r="F46" s="141"/>
-      <c r="G46" s="141"/>
-      <c r="H46" s="230">
+      <c r="A46" s="140" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" s="140"/>
+      <c r="C46" s="140"/>
+      <c r="D46" s="140"/>
+      <c r="E46" s="140"/>
+      <c r="F46" s="140"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="73">
         <v>45000</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="141" t="s">
-        <v>147</v>
-      </c>
-      <c r="B47" s="141"/>
-      <c r="C47" s="141"/>
-      <c r="D47" s="141"/>
-      <c r="E47" s="141"/>
-      <c r="F47" s="141"/>
-      <c r="G47" s="141"/>
-      <c r="H47" s="230">
+      <c r="A47" s="140" t="s">
+        <v>145</v>
+      </c>
+      <c r="B47" s="140"/>
+      <c r="C47" s="140"/>
+      <c r="D47" s="140"/>
+      <c r="E47" s="140"/>
+      <c r="F47" s="140"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="73">
         <v>50050</v>
       </c>
       <c r="J47" s="6"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="141" t="s">
+      <c r="A48" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="B48" s="141"/>
-      <c r="C48" s="141"/>
-      <c r="D48" s="141"/>
-      <c r="E48" s="141"/>
-      <c r="F48" s="141"/>
-      <c r="G48" s="141"/>
-      <c r="H48" s="70">
+      <c r="B48" s="140"/>
+      <c r="C48" s="140"/>
+      <c r="D48" s="140"/>
+      <c r="E48" s="140"/>
+      <c r="F48" s="140"/>
+      <c r="G48" s="140"/>
+      <c r="H48" s="69">
         <f>SUM(H41:H47)</f>
         <v>368324.91000000003</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="196" t="s">
-        <v>139</v>
-      </c>
-      <c r="B49" s="196"/>
-      <c r="C49" s="196"/>
-      <c r="D49" s="196"/>
-      <c r="E49" s="196"/>
-      <c r="F49" s="196"/>
-      <c r="G49" s="196"/>
-      <c r="H49" s="196"/>
+      <c r="A49" s="227" t="s">
+        <v>138</v>
+      </c>
+      <c r="B49" s="227"/>
+      <c r="C49" s="227"/>
+      <c r="D49" s="227"/>
+      <c r="E49" s="227"/>
+      <c r="F49" s="227"/>
+      <c r="G49" s="227"/>
+      <c r="H49" s="227"/>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="141" t="s">
+      <c r="A50" s="140" t="s">
         <v>71</v>
       </c>
-      <c r="B50" s="141"/>
-      <c r="C50" s="141"/>
-      <c r="D50" s="141"/>
-      <c r="E50" s="141"/>
-      <c r="F50" s="141"/>
-      <c r="G50" s="141"/>
-      <c r="H50" s="230">
+      <c r="B50" s="140"/>
+      <c r="C50" s="140"/>
+      <c r="D50" s="140"/>
+      <c r="E50" s="140"/>
+      <c r="F50" s="140"/>
+      <c r="G50" s="140"/>
+      <c r="H50" s="73">
         <v>156900</v>
       </c>
       <c r="J50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="141" t="s">
-        <v>121</v>
-      </c>
-      <c r="B51" s="141"/>
-      <c r="C51" s="141"/>
-      <c r="D51" s="141"/>
-      <c r="E51" s="141"/>
-      <c r="F51" s="141"/>
-      <c r="G51" s="141"/>
-      <c r="H51" s="230">
+      <c r="A51" s="140" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" s="140"/>
+      <c r="C51" s="140"/>
+      <c r="D51" s="140"/>
+      <c r="E51" s="140"/>
+      <c r="F51" s="140"/>
+      <c r="G51" s="140"/>
+      <c r="H51" s="73">
         <v>35000</v>
       </c>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" s="141"/>
-      <c r="B52" s="141"/>
-      <c r="C52" s="141"/>
-      <c r="D52" s="141"/>
-      <c r="E52" s="141"/>
-      <c r="F52" s="141"/>
-      <c r="G52" s="141"/>
-      <c r="H52" s="74"/>
+      <c r="A52" s="140"/>
+      <c r="B52" s="140"/>
+      <c r="C52" s="140"/>
+      <c r="D52" s="140"/>
+      <c r="E52" s="140"/>
+      <c r="F52" s="140"/>
+      <c r="G52" s="140"/>
+      <c r="H52" s="73"/>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="141" t="s">
+      <c r="A53" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="B53" s="141"/>
-      <c r="C53" s="141"/>
-      <c r="D53" s="141"/>
-      <c r="E53" s="141"/>
-      <c r="F53" s="141"/>
-      <c r="G53" s="141"/>
-      <c r="H53" s="181">
+      <c r="B53" s="140"/>
+      <c r="C53" s="140"/>
+      <c r="D53" s="140"/>
+      <c r="E53" s="140"/>
+      <c r="F53" s="140"/>
+      <c r="G53" s="140"/>
+      <c r="H53" s="180">
         <f>SUM(H50:H52)</f>
         <v>191900</v>
       </c>
       <c r="K53" s="7"/>
     </row>
     <row r="54" spans="1:11" s="6" customFormat="1">
-      <c r="A54" s="198" t="s">
-        <v>140</v>
-      </c>
-      <c r="B54" s="199"/>
-      <c r="C54" s="199"/>
-      <c r="D54" s="199"/>
-      <c r="E54" s="199"/>
-      <c r="F54" s="199"/>
-      <c r="G54" s="199"/>
-      <c r="H54" s="200"/>
+      <c r="A54" s="228" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" s="229"/>
+      <c r="C54" s="229"/>
+      <c r="D54" s="229"/>
+      <c r="E54" s="229"/>
+      <c r="F54" s="229"/>
+      <c r="G54" s="229"/>
+      <c r="H54" s="230"/>
     </row>
     <row r="55" spans="1:11" s="6" customFormat="1">
-      <c r="A55" s="81" t="s">
-        <v>123</v>
-      </c>
-      <c r="B55" s="81"/>
-      <c r="C55" s="81"/>
-      <c r="D55" s="81"/>
-      <c r="E55" s="81"/>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="230">
+      <c r="A55" s="80" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="80"/>
+      <c r="C55" s="80"/>
+      <c r="D55" s="80"/>
+      <c r="E55" s="80"/>
+      <c r="F55" s="80"/>
+      <c r="G55" s="80"/>
+      <c r="H55" s="73">
         <v>24990</v>
       </c>
       <c r="I55" s="60"/>
     </row>
     <row r="56" spans="1:11" s="6" customFormat="1">
-      <c r="A56" s="81" t="s">
+      <c r="A56" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="B56" s="81"/>
-      <c r="C56" s="81"/>
-      <c r="D56" s="81"/>
-      <c r="E56" s="81"/>
-      <c r="F56" s="81"/>
-      <c r="G56" s="81"/>
-      <c r="H56" s="70">
+      <c r="B56" s="80"/>
+      <c r="C56" s="80"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="80"/>
+      <c r="F56" s="80"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="69">
         <f>SUM(H55)</f>
         <v>24990</v>
       </c>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1">
-      <c r="A57" s="196" t="s">
-        <v>141</v>
-      </c>
-      <c r="B57" s="196"/>
-      <c r="C57" s="196"/>
-      <c r="D57" s="196"/>
-      <c r="E57" s="196"/>
-      <c r="F57" s="196"/>
-      <c r="G57" s="196"/>
-      <c r="H57" s="196"/>
+      <c r="A57" s="227" t="s">
+        <v>140</v>
+      </c>
+      <c r="B57" s="227"/>
+      <c r="C57" s="227"/>
+      <c r="D57" s="227"/>
+      <c r="E57" s="227"/>
+      <c r="F57" s="227"/>
+      <c r="G57" s="227"/>
+      <c r="H57" s="227"/>
     </row>
     <row r="58" spans="1:11" s="6" customFormat="1">
-      <c r="A58" s="81"/>
-      <c r="B58" s="81"/>
-      <c r="C58" s="81"/>
-      <c r="D58" s="81"/>
-      <c r="E58" s="81"/>
-      <c r="F58" s="81"/>
-      <c r="G58" s="81"/>
-      <c r="H58" s="74"/>
+      <c r="A58" s="80" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" s="80"/>
+      <c r="C58" s="80"/>
+      <c r="D58" s="80"/>
+      <c r="E58" s="80"/>
+      <c r="F58" s="80"/>
+      <c r="G58" s="80"/>
+      <c r="H58" s="73">
+        <v>1959024</v>
+      </c>
     </row>
     <row r="59" spans="1:11" s="6" customFormat="1">
-      <c r="A59" s="177"/>
-      <c r="B59" s="177"/>
-      <c r="C59" s="177"/>
-      <c r="D59" s="177"/>
-      <c r="E59" s="177"/>
-      <c r="F59" s="177"/>
-      <c r="G59" s="177"/>
-      <c r="H59" s="176"/>
+      <c r="A59" s="80" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" s="80"/>
+      <c r="C59" s="80"/>
+      <c r="D59" s="80"/>
+      <c r="E59" s="80"/>
+      <c r="F59" s="80"/>
+      <c r="G59" s="80"/>
+      <c r="H59" s="73">
+        <v>100000</v>
+      </c>
     </row>
     <row r="60" spans="1:11" s="6" customFormat="1">
-      <c r="A60" s="177"/>
-      <c r="B60" s="177"/>
-      <c r="C60" s="177"/>
-      <c r="D60" s="177"/>
-      <c r="E60" s="177"/>
-      <c r="F60" s="177"/>
-      <c r="G60" s="177"/>
-      <c r="H60" s="176">
+      <c r="A60" s="176"/>
+      <c r="B60" s="176"/>
+      <c r="C60" s="176"/>
+      <c r="D60" s="176"/>
+      <c r="E60" s="176"/>
+      <c r="F60" s="176"/>
+      <c r="G60" s="176"/>
+      <c r="H60" s="175">
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A61" s="81" t="s">
+      <c r="A61" s="80" t="s">
         <v>76</v>
       </c>
-      <c r="B61" s="81"/>
-      <c r="C61" s="81"/>
-      <c r="D61" s="81"/>
-      <c r="E61" s="81"/>
-      <c r="F61" s="81"/>
-      <c r="G61" s="81"/>
-      <c r="H61" s="70">
+      <c r="B61" s="80"/>
+      <c r="C61" s="80"/>
+      <c r="D61" s="80"/>
+      <c r="E61" s="80"/>
+      <c r="F61" s="80"/>
+      <c r="G61" s="80"/>
+      <c r="H61" s="69">
         <f>SUM(H58:H60)</f>
-        <v>0</v>
+        <v>2059024</v>
       </c>
       <c r="I61" s="60"/>
     </row>
     <row r="62" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A62" s="198"/>
-      <c r="B62" s="199"/>
-      <c r="C62" s="199"/>
-      <c r="D62" s="199"/>
-      <c r="E62" s="199"/>
-      <c r="F62" s="199"/>
-      <c r="G62" s="199"/>
-      <c r="H62" s="200"/>
+      <c r="A62" s="228"/>
+      <c r="B62" s="229"/>
+      <c r="C62" s="229"/>
+      <c r="D62" s="229"/>
+      <c r="E62" s="229"/>
+      <c r="F62" s="229"/>
+      <c r="G62" s="229"/>
+      <c r="H62" s="230"/>
     </row>
     <row r="63" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A63" s="82"/>
-      <c r="B63" s="83"/>
-      <c r="C63" s="83"/>
-      <c r="D63" s="83"/>
-      <c r="E63" s="83"/>
-      <c r="F63" s="83"/>
-      <c r="G63" s="83"/>
-      <c r="H63" s="160">
+      <c r="A63" s="81"/>
+      <c r="B63" s="82"/>
+      <c r="C63" s="82"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="82"/>
+      <c r="F63" s="82"/>
+      <c r="G63" s="82"/>
+      <c r="H63" s="159">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A64" s="161"/>
-      <c r="B64" s="162"/>
-      <c r="C64" s="162"/>
-      <c r="D64" s="162"/>
-      <c r="E64" s="162"/>
-      <c r="F64" s="162"/>
-      <c r="G64" s="162"/>
-      <c r="H64" s="163">
+      <c r="A64" s="160"/>
+      <c r="B64" s="161"/>
+      <c r="C64" s="161"/>
+      <c r="D64" s="161"/>
+      <c r="E64" s="161"/>
+      <c r="F64" s="161"/>
+      <c r="G64" s="161"/>
+      <c r="H64" s="162">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A65" s="164"/>
-      <c r="B65" s="165"/>
-      <c r="C65" s="165"/>
-      <c r="D65" s="165"/>
-      <c r="E65" s="165"/>
-      <c r="F65" s="165"/>
-      <c r="G65" s="165"/>
-      <c r="H65" s="160">
+      <c r="A65" s="163"/>
+      <c r="B65" s="164"/>
+      <c r="C65" s="164"/>
+      <c r="D65" s="164"/>
+      <c r="E65" s="164"/>
+      <c r="F65" s="164"/>
+      <c r="G65" s="164"/>
+      <c r="H65" s="159">
         <f>H63+H64</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
       <c r="A66" s="209" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B66" s="210"/>
       <c r="C66" s="210"/>
@@ -3066,171 +3086,171 @@
       <c r="E66" s="210"/>
       <c r="F66" s="210"/>
       <c r="G66" s="210"/>
-      <c r="H66" s="166">
+      <c r="H66" s="165">
         <f>H61</f>
-        <v>0</v>
+        <v>2059024</v>
       </c>
     </row>
     <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A67" s="212"/>
-      <c r="B67" s="212"/>
-      <c r="C67" s="212"/>
-      <c r="D67" s="212"/>
-      <c r="E67" s="212"/>
-      <c r="F67" s="212"/>
-      <c r="G67" s="212"/>
-      <c r="H67" s="212"/>
+      <c r="A67" s="214"/>
+      <c r="B67" s="214"/>
+      <c r="C67" s="214"/>
+      <c r="D67" s="214"/>
+      <c r="E67" s="214"/>
+      <c r="F67" s="214"/>
+      <c r="G67" s="214"/>
+      <c r="H67" s="214"/>
     </row>
     <row r="68" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A68" s="213"/>
-      <c r="B68" s="213"/>
-      <c r="C68" s="213"/>
-      <c r="D68" s="213"/>
-      <c r="E68" s="213"/>
-      <c r="F68" s="213"/>
-      <c r="G68" s="213"/>
-      <c r="H68" s="213"/>
+      <c r="A68" s="215"/>
+      <c r="B68" s="215"/>
+      <c r="C68" s="215"/>
+      <c r="D68" s="215"/>
+      <c r="E68" s="215"/>
+      <c r="F68" s="215"/>
+      <c r="G68" s="215"/>
+      <c r="H68" s="215"/>
     </row>
     <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A69" s="211" t="s">
-        <v>86</v>
-      </c>
-      <c r="B69" s="211"/>
-      <c r="C69" s="211"/>
-      <c r="D69" s="211"/>
-      <c r="E69" s="211"/>
-      <c r="F69" s="211"/>
-      <c r="G69" s="211"/>
-      <c r="H69" s="167"/>
+      <c r="A69" s="213" t="s">
+        <v>85</v>
+      </c>
+      <c r="B69" s="213"/>
+      <c r="C69" s="213"/>
+      <c r="D69" s="213"/>
+      <c r="E69" s="213"/>
+      <c r="F69" s="213"/>
+      <c r="G69" s="213"/>
+      <c r="H69" s="166"/>
     </row>
     <row r="70" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A70" s="219"/>
-      <c r="B70" s="220"/>
-      <c r="C70" s="220"/>
-      <c r="D70" s="220"/>
-      <c r="E70" s="220"/>
-      <c r="F70" s="220"/>
-      <c r="G70" s="221"/>
-      <c r="H70" s="74"/>
+      <c r="A70" s="198"/>
+      <c r="B70" s="199"/>
+      <c r="C70" s="199"/>
+      <c r="D70" s="199"/>
+      <c r="E70" s="199"/>
+      <c r="F70" s="199"/>
+      <c r="G70" s="200"/>
+      <c r="H70" s="73"/>
     </row>
     <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A71" s="131" t="s">
+      <c r="A71" s="130" t="s">
         <v>75</v>
       </c>
-      <c r="B71" s="81"/>
-      <c r="C71" s="81"/>
-      <c r="D71" s="81"/>
-      <c r="E71" s="81"/>
-      <c r="F71" s="81"/>
-      <c r="G71" s="81"/>
-      <c r="H71" s="70">
+      <c r="B71" s="80"/>
+      <c r="C71" s="80"/>
+      <c r="D71" s="80"/>
+      <c r="E71" s="80"/>
+      <c r="F71" s="80"/>
+      <c r="G71" s="80"/>
+      <c r="H71" s="69">
         <f>SUM(H70:H70)</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A72" s="132"/>
-      <c r="B72" s="132"/>
-      <c r="C72" s="132"/>
-      <c r="D72" s="132"/>
-      <c r="E72" s="132"/>
-      <c r="F72" s="132"/>
-      <c r="G72" s="132"/>
-      <c r="H72" s="133"/>
+      <c r="A72" s="131"/>
+      <c r="B72" s="131"/>
+      <c r="C72" s="131"/>
+      <c r="D72" s="131"/>
+      <c r="E72" s="131"/>
+      <c r="F72" s="131"/>
+      <c r="G72" s="131"/>
+      <c r="H72" s="132"/>
     </row>
     <row r="73" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A73" s="192" t="s">
-        <v>85</v>
-      </c>
-      <c r="B73" s="193"/>
-      <c r="C73" s="193"/>
-      <c r="D73" s="193"/>
-      <c r="E73" s="193"/>
-      <c r="F73" s="193"/>
-      <c r="G73" s="193"/>
-      <c r="H73" s="134">
+      <c r="A73" s="211" t="s">
+        <v>84</v>
+      </c>
+      <c r="B73" s="212"/>
+      <c r="C73" s="212"/>
+      <c r="D73" s="212"/>
+      <c r="E73" s="212"/>
+      <c r="F73" s="212"/>
+      <c r="G73" s="212"/>
+      <c r="H73" s="133">
         <f>H71</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A74" s="204" t="s">
+      <c r="A74" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74" s="194"/>
+      <c r="C74" s="194"/>
+      <c r="D74" s="194"/>
+      <c r="E74" s="194"/>
+      <c r="F74" s="194"/>
+      <c r="G74" s="195"/>
+      <c r="H74" s="133"/>
+    </row>
+    <row r="75" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A75" s="193" t="s">
+        <v>95</v>
+      </c>
+      <c r="B75" s="194"/>
+      <c r="C75" s="194"/>
+      <c r="D75" s="194"/>
+      <c r="E75" s="194"/>
+      <c r="F75" s="194"/>
+      <c r="G75" s="195"/>
+      <c r="H75" s="133"/>
+    </row>
+    <row r="76" spans="1:11" ht="18.75">
+      <c r="A76" s="211" t="s">
         <v>91</v>
       </c>
-      <c r="B74" s="205"/>
-      <c r="C74" s="205"/>
-      <c r="D74" s="205"/>
-      <c r="E74" s="205"/>
-      <c r="F74" s="205"/>
-      <c r="G74" s="206"/>
-      <c r="H74" s="134"/>
-    </row>
-    <row r="75" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A75" s="204" t="s">
-        <v>96</v>
-      </c>
-      <c r="B75" s="205"/>
-      <c r="C75" s="205"/>
-      <c r="D75" s="205"/>
-      <c r="E75" s="205"/>
-      <c r="F75" s="205"/>
-      <c r="G75" s="206"/>
-      <c r="H75" s="134"/>
-    </row>
-    <row r="76" spans="1:11" ht="18.75">
-      <c r="A76" s="192" t="s">
-        <v>92</v>
-      </c>
-      <c r="B76" s="193"/>
-      <c r="C76" s="193"/>
-      <c r="D76" s="193"/>
-      <c r="E76" s="193"/>
-      <c r="F76" s="193"/>
-      <c r="G76" s="193"/>
-      <c r="H76" s="134">
+      <c r="B76" s="212"/>
+      <c r="C76" s="212"/>
+      <c r="D76" s="212"/>
+      <c r="E76" s="212"/>
+      <c r="F76" s="212"/>
+      <c r="G76" s="212"/>
+      <c r="H76" s="133">
         <f>H30+H39+H48+H53+H56+H35+H18+H26</f>
         <v>3101073.62</v>
       </c>
-      <c r="J76" s="175"/>
-      <c r="K76" s="146"/>
+      <c r="J76" s="174"/>
+      <c r="K76" s="145"/>
     </row>
     <row r="77" spans="1:11" ht="18.75">
-      <c r="A77" s="201" t="s">
-        <v>126</v>
-      </c>
-      <c r="B77" s="202"/>
-      <c r="C77" s="202"/>
-      <c r="D77" s="202"/>
-      <c r="E77" s="202"/>
-      <c r="F77" s="202"/>
-      <c r="G77" s="203"/>
-      <c r="H77" s="135">
+      <c r="A77" s="204" t="s">
+        <v>125</v>
+      </c>
+      <c r="B77" s="205"/>
+      <c r="C77" s="205"/>
+      <c r="D77" s="205"/>
+      <c r="E77" s="205"/>
+      <c r="F77" s="205"/>
+      <c r="G77" s="206"/>
+      <c r="H77" s="134">
         <f>H74+H76</f>
         <v>3101073.62</v>
       </c>
-      <c r="I77" s="130"/>
-      <c r="J77" s="182"/>
-      <c r="K77" s="182"/>
+      <c r="I77" s="129"/>
+      <c r="J77" s="216"/>
+      <c r="K77" s="216"/>
     </row>
     <row r="78" spans="1:11" ht="18.75">
-      <c r="A78" s="201" t="s">
-        <v>97</v>
-      </c>
-      <c r="B78" s="202"/>
-      <c r="C78" s="202"/>
-      <c r="D78" s="202"/>
-      <c r="E78" s="202"/>
-      <c r="F78" s="202"/>
-      <c r="G78" s="203"/>
-      <c r="H78" s="136">
+      <c r="A78" s="204" t="s">
+        <v>96</v>
+      </c>
+      <c r="B78" s="205"/>
+      <c r="C78" s="205"/>
+      <c r="D78" s="205"/>
+      <c r="E78" s="205"/>
+      <c r="F78" s="205"/>
+      <c r="G78" s="206"/>
+      <c r="H78" s="135">
         <f>H75+H73</f>
         <v>0</v>
       </c>
-      <c r="J78" s="146"/>
+      <c r="J78" s="145"/>
     </row>
     <row r="79" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A79" s="207" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B79" s="208"/>
       <c r="C79" s="208"/>
@@ -3238,254 +3258,259 @@
       <c r="E79" s="208"/>
       <c r="F79" s="208"/>
       <c r="G79" s="208"/>
-      <c r="H79" s="137">
+      <c r="H79" s="136">
         <f>H76+H73</f>
         <v>3101073.62</v>
       </c>
       <c r="J79" s="7"/>
     </row>
     <row r="80" spans="1:11" ht="18.75" hidden="1">
-      <c r="A80" s="194" t="s">
+      <c r="A80" s="225" t="s">
         <v>17</v>
       </c>
-      <c r="B80" s="195"/>
-      <c r="C80" s="195"/>
-      <c r="D80" s="195"/>
-      <c r="E80" s="195"/>
-      <c r="F80" s="195"/>
-      <c r="G80" s="195"/>
-      <c r="H80" s="138">
+      <c r="B80" s="226"/>
+      <c r="C80" s="226"/>
+      <c r="D80" s="226"/>
+      <c r="E80" s="226"/>
+      <c r="F80" s="226"/>
+      <c r="G80" s="226"/>
+      <c r="H80" s="137">
         <f>H65</f>
         <v>0</v>
       </c>
       <c r="J80" s="7"/>
     </row>
     <row r="81" spans="1:11" ht="18.75" hidden="1">
-      <c r="A81" s="139"/>
-      <c r="B81" s="139"/>
-      <c r="C81" s="139"/>
-      <c r="D81" s="139"/>
-      <c r="E81" s="139"/>
-      <c r="F81" s="139"/>
-      <c r="G81" s="139"/>
-      <c r="H81" s="140"/>
+      <c r="A81" s="138"/>
+      <c r="B81" s="138"/>
+      <c r="C81" s="138"/>
+      <c r="D81" s="138"/>
+      <c r="E81" s="138"/>
+      <c r="F81" s="138"/>
+      <c r="G81" s="138"/>
+      <c r="H81" s="139"/>
       <c r="J81" s="7"/>
     </row>
     <row r="82" spans="1:11" ht="18.75" hidden="1">
-      <c r="A82" s="139"/>
-      <c r="B82" s="139"/>
-      <c r="C82" s="139"/>
-      <c r="D82" s="139"/>
-      <c r="E82" s="139"/>
-      <c r="F82" s="139"/>
-      <c r="G82" s="139"/>
-      <c r="H82" s="140"/>
+      <c r="A82" s="138"/>
+      <c r="B82" s="138"/>
+      <c r="C82" s="138"/>
+      <c r="D82" s="138"/>
+      <c r="E82" s="138"/>
+      <c r="F82" s="138"/>
+      <c r="G82" s="138"/>
+      <c r="H82" s="139"/>
       <c r="J82" s="7"/>
     </row>
     <row r="83" spans="1:11" ht="18.75" hidden="1">
-      <c r="A83" s="139"/>
-      <c r="B83" s="139"/>
-      <c r="C83" s="139"/>
-      <c r="D83" s="139"/>
-      <c r="E83" s="139"/>
-      <c r="F83" s="139"/>
-      <c r="G83" s="139"/>
-      <c r="H83" s="140"/>
+      <c r="A83" s="138"/>
+      <c r="B83" s="138"/>
+      <c r="C83" s="138"/>
+      <c r="D83" s="138"/>
+      <c r="E83" s="138"/>
+      <c r="F83" s="138"/>
+      <c r="G83" s="138"/>
+      <c r="H83" s="139"/>
       <c r="J83" s="7"/>
     </row>
     <row r="84" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A84" s="141"/>
-      <c r="B84" s="141"/>
-      <c r="C84" s="141"/>
-      <c r="D84" s="141"/>
-      <c r="E84" s="141"/>
-      <c r="F84" s="141"/>
-      <c r="G84" s="141"/>
-      <c r="H84" s="141"/>
+      <c r="A84" s="140"/>
+      <c r="B84" s="140"/>
+      <c r="C84" s="140"/>
+      <c r="D84" s="140"/>
+      <c r="E84" s="140"/>
+      <c r="F84" s="140"/>
+      <c r="G84" s="140"/>
+      <c r="H84" s="140"/>
     </row>
     <row r="85" spans="1:11" ht="18.75">
-      <c r="A85" s="187" t="s">
+      <c r="A85" s="220" t="s">
         <v>10</v>
       </c>
-      <c r="B85" s="188"/>
-      <c r="C85" s="188"/>
-      <c r="D85" s="188"/>
-      <c r="E85" s="188"/>
-      <c r="F85" s="188"/>
-      <c r="G85" s="188"/>
-      <c r="H85" s="189"/>
+      <c r="B85" s="221"/>
+      <c r="C85" s="221"/>
+      <c r="D85" s="221"/>
+      <c r="E85" s="221"/>
+      <c r="F85" s="221"/>
+      <c r="G85" s="221"/>
+      <c r="H85" s="222"/>
     </row>
     <row r="86" spans="1:11" ht="18.75">
-      <c r="A86" s="142" t="s">
+      <c r="A86" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="B86" s="143"/>
-      <c r="C86" s="143"/>
-      <c r="D86" s="143"/>
-      <c r="E86" s="143"/>
-      <c r="F86" s="143"/>
-      <c r="G86" s="143"/>
-      <c r="H86" s="144">
+      <c r="B86" s="142"/>
+      <c r="C86" s="142"/>
+      <c r="D86" s="142"/>
+      <c r="E86" s="142"/>
+      <c r="F86" s="142"/>
+      <c r="G86" s="142"/>
+      <c r="H86" s="143">
         <v>4403223.2156698657</v>
       </c>
     </row>
     <row r="87" spans="1:11">
-      <c r="A87" s="82" t="s">
-        <v>135</v>
-      </c>
-      <c r="B87" s="83"/>
-      <c r="C87" s="83"/>
-      <c r="D87" s="83"/>
-      <c r="E87" s="83"/>
-      <c r="F87" s="83"/>
-      <c r="G87" s="83"/>
-      <c r="H87" s="145">
+      <c r="A87" s="81" t="s">
+        <v>134</v>
+      </c>
+      <c r="B87" s="82"/>
+      <c r="C87" s="82"/>
+      <c r="D87" s="82"/>
+      <c r="E87" s="82"/>
+      <c r="F87" s="82"/>
+      <c r="G87" s="82"/>
+      <c r="H87" s="144">
         <f>Planilla!G32</f>
-        <v>2657237.8350200001</v>
+        <v>3704102.8142494997</v>
       </c>
     </row>
     <row r="88" spans="1:11">
-      <c r="A88" s="79" t="s">
-        <v>154</v>
-      </c>
-      <c r="B88" s="80"/>
-      <c r="C88" s="80"/>
-      <c r="D88" s="80"/>
-      <c r="E88" s="80"/>
-      <c r="F88" s="80"/>
-      <c r="G88" s="80"/>
-      <c r="H88" s="69">
+      <c r="A88" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="B88" s="79"/>
+      <c r="C88" s="79"/>
+      <c r="D88" s="79"/>
+      <c r="E88" s="79"/>
+      <c r="F88" s="79"/>
+      <c r="G88" s="79"/>
+      <c r="H88" s="243">
         <f>-(H79)</f>
         <v>-3101073.62</v>
       </c>
     </row>
     <row r="89" spans="1:11">
-      <c r="A89" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="B89" s="80"/>
-      <c r="C89" s="80"/>
-      <c r="D89" s="80"/>
-      <c r="E89" s="80"/>
-      <c r="F89" s="80"/>
-      <c r="G89" s="80"/>
-      <c r="H89" s="69">
+      <c r="A89" s="78" t="s">
+        <v>87</v>
+      </c>
+      <c r="B89" s="79"/>
+      <c r="C89" s="79"/>
+      <c r="D89" s="79"/>
+      <c r="E89" s="79"/>
+      <c r="F89" s="79"/>
+      <c r="G89" s="79"/>
+      <c r="H89" s="243">
         <f>-H66</f>
-        <v>0</v>
+        <v>-2059024</v>
       </c>
       <c r="K89" s="6"/>
     </row>
     <row r="90" spans="1:11">
-      <c r="A90" s="79" t="s">
+      <c r="A90" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="B90" s="80" t="s">
-        <v>118</v>
-      </c>
-      <c r="C90" s="80"/>
-      <c r="D90" s="80"/>
-      <c r="E90" s="80"/>
-      <c r="F90" s="80"/>
-      <c r="G90" s="80"/>
-      <c r="H90" s="125">
+      <c r="B90" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="C90" s="79"/>
+      <c r="D90" s="79"/>
+      <c r="E90" s="79"/>
+      <c r="F90" s="79"/>
+      <c r="G90" s="79"/>
+      <c r="H90" s="124">
         <v>133680</v>
       </c>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" s="79" t="s">
+      <c r="A91" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="B91" s="80"/>
-      <c r="C91" s="80"/>
-      <c r="D91" s="80"/>
-      <c r="E91" s="80"/>
-      <c r="F91" s="80"/>
-      <c r="G91" s="80"/>
-      <c r="H91" s="125">
+      <c r="B91" s="79"/>
+      <c r="C91" s="79"/>
+      <c r="D91" s="79"/>
+      <c r="E91" s="79"/>
+      <c r="F91" s="79"/>
+      <c r="G91" s="79"/>
+      <c r="H91" s="124">
         <f>177000-H90</f>
         <v>43320</v>
       </c>
-      <c r="I91" s="146"/>
+      <c r="I91" s="145"/>
     </row>
     <row r="92" spans="1:11">
-      <c r="A92" s="12" t="s">
+      <c r="A92" s="78" t="s">
+        <v>157</v>
+      </c>
+      <c r="B92" s="79"/>
+      <c r="C92" s="79"/>
+      <c r="D92" s="79"/>
+      <c r="E92" s="79"/>
+      <c r="F92" s="79"/>
+      <c r="G92" s="79"/>
+      <c r="H92" s="242">
+        <v>-1000000</v>
+      </c>
+      <c r="I92" s="145"/>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B93" s="83"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="98"/>
+    </row>
+    <row r="94" spans="1:11" ht="18.75">
+      <c r="A94" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B94" s="23"/>
+      <c r="C94" s="23"/>
+      <c r="D94" s="23"/>
+      <c r="E94" s="23"/>
+      <c r="F94" s="23"/>
+      <c r="G94" s="23"/>
+      <c r="H94" s="84">
+        <f>SUM(H86:H93)</f>
+        <v>2124228.4099193653</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="96" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A96" s="217" t="s">
+        <v>100</v>
+      </c>
+      <c r="B96" s="218"/>
+      <c r="C96" s="218"/>
+      <c r="D96" s="218"/>
+      <c r="E96" s="218"/>
+      <c r="F96" s="218"/>
+      <c r="G96" s="218"/>
+      <c r="H96" s="219"/>
+    </row>
+    <row r="97" spans="1:8" ht="15.75">
+      <c r="A97" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B97" s="87"/>
+      <c r="C97" s="87"/>
+      <c r="D97" s="87"/>
+      <c r="E97" s="87"/>
+      <c r="F97" s="87"/>
+      <c r="G97" s="87"/>
+      <c r="H97" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="B92" s="84"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="99"/>
-    </row>
-    <row r="93" spans="1:11" ht="18.75">
-      <c r="A93" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B93" s="23"/>
-      <c r="C93" s="23"/>
-      <c r="D93" s="23"/>
-      <c r="E93" s="23"/>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
-      <c r="H93" s="85">
-        <f>SUM(H86:H92)</f>
-        <v>4136387.4306898657</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="15.75" thickBot="1"/>
-    <row r="95" spans="1:11" ht="16.5" thickBot="1">
-      <c r="A95" s="184" t="s">
-        <v>101</v>
-      </c>
-      <c r="B95" s="185"/>
-      <c r="C95" s="185"/>
-      <c r="D95" s="185"/>
-      <c r="E95" s="185"/>
-      <c r="F95" s="185"/>
-      <c r="G95" s="185"/>
-      <c r="H95" s="186"/>
-    </row>
-    <row r="96" spans="1:11" ht="15.75">
-      <c r="A96" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="B96" s="88"/>
-      <c r="C96" s="88"/>
-      <c r="D96" s="88"/>
-      <c r="E96" s="88"/>
-      <c r="F96" s="88"/>
-      <c r="G96" s="88"/>
-      <c r="H96" s="89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="61" t="s">
-        <v>125</v>
-      </c>
-      <c r="B97" s="92"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="61"/>
-      <c r="E97" s="61"/>
-      <c r="F97" s="61"/>
-      <c r="G97" s="61"/>
-      <c r="H97" s="129"/>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="61"/>
-      <c r="B98" s="98"/>
-      <c r="C98" s="61"/>
+      <c r="B98" s="91"/>
+      <c r="C98" s="4"/>
       <c r="D98" s="61"/>
       <c r="E98" s="61"/>
       <c r="F98" s="61"/>
       <c r="G98" s="61"/>
-      <c r="H98" s="21"/>
+      <c r="H98" s="128"/>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="61"/>
-      <c r="B99" s="61"/>
+      <c r="B99" s="97"/>
       <c r="C99" s="61"/>
       <c r="D99" s="61"/>
       <c r="E99" s="61"/>
@@ -3494,78 +3519,75 @@
       <c r="H99" s="21"/>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="86" t="s">
+      <c r="A100" s="61"/>
+      <c r="B100" s="61"/>
+      <c r="C100" s="61"/>
+      <c r="D100" s="61"/>
+      <c r="E100" s="61"/>
+      <c r="F100" s="61"/>
+      <c r="G100" s="61"/>
+      <c r="H100" s="21"/>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="B100" s="86"/>
-      <c r="C100" s="86"/>
-      <c r="D100" s="86"/>
-      <c r="E100" s="86"/>
-      <c r="F100" s="86"/>
-      <c r="G100" s="86"/>
-      <c r="H100" s="87">
-        <f>SUM(H96:H99)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" hidden="1">
-      <c r="A103" s="183"/>
-      <c r="B103" s="183"/>
-      <c r="C103" s="183"/>
-      <c r="D103" s="183"/>
-      <c r="E103" s="183"/>
-      <c r="F103" s="183"/>
-      <c r="G103" s="183"/>
-      <c r="H103" s="183"/>
+      <c r="B101" s="85"/>
+      <c r="C101" s="85"/>
+      <c r="D101" s="85"/>
+      <c r="E101" s="85"/>
+      <c r="F101" s="85"/>
+      <c r="G101" s="85"/>
+      <c r="H101" s="86">
+        <f>SUM(H97:H100)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="104" spans="1:8" hidden="1">
-      <c r="A104" s="183"/>
-      <c r="B104" s="183"/>
-      <c r="C104" s="183"/>
-      <c r="D104" s="183"/>
-      <c r="E104" s="183"/>
-      <c r="F104" s="183"/>
-      <c r="G104" s="183"/>
-      <c r="H104" s="183"/>
+      <c r="A104" s="202"/>
+      <c r="B104" s="202"/>
+      <c r="C104" s="202"/>
+      <c r="D104" s="202"/>
+      <c r="E104" s="202"/>
+      <c r="F104" s="202"/>
+      <c r="G104" s="202"/>
+      <c r="H104" s="202"/>
     </row>
     <row r="105" spans="1:8" hidden="1">
-      <c r="A105" s="183"/>
-      <c r="B105" s="183"/>
-      <c r="C105" s="183"/>
-      <c r="D105" s="183"/>
-      <c r="E105" s="183"/>
-      <c r="F105" s="183"/>
-      <c r="G105" s="183"/>
-      <c r="H105" s="183"/>
+      <c r="A105" s="202"/>
+      <c r="B105" s="202"/>
+      <c r="C105" s="202"/>
+      <c r="D105" s="202"/>
+      <c r="E105" s="202"/>
+      <c r="F105" s="202"/>
+      <c r="G105" s="202"/>
+      <c r="H105" s="202"/>
     </row>
     <row r="106" spans="1:8" hidden="1">
-      <c r="A106" s="183"/>
-      <c r="B106" s="183"/>
-      <c r="C106" s="183"/>
-      <c r="D106" s="183"/>
-      <c r="E106" s="183"/>
-      <c r="F106" s="183"/>
-      <c r="G106" s="183"/>
-      <c r="H106" s="183"/>
+      <c r="A106" s="202"/>
+      <c r="B106" s="202"/>
+      <c r="C106" s="202"/>
+      <c r="D106" s="202"/>
+      <c r="E106" s="202"/>
+      <c r="F106" s="202"/>
+      <c r="G106" s="202"/>
+      <c r="H106" s="202"/>
+    </row>
+    <row r="107" spans="1:8" hidden="1">
+      <c r="A107" s="202"/>
+      <c r="B107" s="202"/>
+      <c r="C107" s="202"/>
+      <c r="D107" s="202"/>
+      <c r="E107" s="202"/>
+      <c r="F107" s="202"/>
+      <c r="G107" s="202"/>
+      <c r="H107" s="202"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A67:H68"/>
     <mergeCell ref="J77:K77"/>
-    <mergeCell ref="A103:H106"/>
-    <mergeCell ref="A95:H95"/>
+    <mergeCell ref="A104:H107"/>
+    <mergeCell ref="A96:H96"/>
     <mergeCell ref="A85:H85"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="A76:G76"/>
@@ -3579,6 +3601,19 @@
     <mergeCell ref="A62:H62"/>
     <mergeCell ref="A78:G78"/>
     <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A67:H68"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A12:H12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3608,61 +3643,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="26.25" customHeight="1">
-      <c r="A1" s="103"/>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="105" t="s">
+      <c r="A1" s="102"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="104" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="106" t="str">
+      <c r="F1" s="105" t="str">
         <f>RESUMEN!F8</f>
         <v>OCTUBRE</v>
       </c>
-      <c r="G1" s="107"/>
-      <c r="H1" s="105" t="str">
+      <c r="G1" s="106"/>
+      <c r="H1" s="104" t="str">
         <f>RESUMEN!G8</f>
-        <v>VTO: 14/11</v>
-      </c>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-      <c r="N1" s="108"/>
+        <v>VTO: 30/11</v>
+      </c>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="107"/>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="61"/>
       <c r="B2" s="61"/>
-      <c r="C2" s="128">
+      <c r="C2" s="127">
         <v>1333150</v>
       </c>
       <c r="D2" s="61"/>
       <c r="E2" s="61"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
       <c r="L2" s="61"/>
       <c r="M2" s="61"/>
       <c r="N2" s="61"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="116"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="102">
-        <v>3130261.15</v>
+      <c r="A3" s="115"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="101">
+        <v>3101073.62</v>
       </c>
       <c r="D3" s="61"/>
       <c r="E3" s="61"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="118"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="118"/>
-      <c r="K3" s="118"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="K3" s="117"/>
       <c r="L3" s="61" t="s">
         <v>79</v>
       </c>
@@ -3670,21 +3705,24 @@
       <c r="N3" s="61"/>
     </row>
     <row r="4" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A4" s="119"/>
-      <c r="B4" s="120" t="s">
+      <c r="A4" s="118"/>
+      <c r="B4" s="119" t="s">
         <v>80</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="61"/>
-      <c r="E4" s="120" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="124"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
+      <c r="E4" s="119" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="123">
+        <f>3000+102550+102</f>
+        <v>105652</v>
+      </c>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
       <c r="L4" s="61" t="s">
         <v>78</v>
       </c>
@@ -3692,133 +3730,139 @@
       <c r="N4" s="61"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A5" s="121"/>
-      <c r="B5" s="225">
+      <c r="A5" s="120"/>
+      <c r="B5" s="232">
         <f>C3</f>
-        <v>3130261.15</v>
-      </c>
-      <c r="C5" s="225"/>
+        <v>3101073.62</v>
+      </c>
+      <c r="C5" s="232"/>
       <c r="D5" s="21"/>
-      <c r="E5" s="122">
+      <c r="E5" s="121">
         <v>70000</v>
       </c>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="115"/>
-      <c r="K5" s="115"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="114"/>
+      <c r="K5" s="114"/>
       <c r="L5" s="61"/>
       <c r="M5" s="61"/>
       <c r="N5" s="61"/>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A6" s="121"/>
-      <c r="B6" s="123" t="s">
-        <v>81</v>
+      <c r="A6" s="120"/>
+      <c r="B6" s="122" t="s">
+        <v>159</v>
       </c>
       <c r="C6" s="21"/>
       <c r="D6" s="21"/>
-      <c r="E6" s="120" t="s">
-        <v>105</v>
-      </c>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
+      <c r="E6" s="119" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" s="114"/>
+      <c r="G6" s="114"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
       <c r="L6" s="61"/>
       <c r="M6" s="61"/>
       <c r="N6" s="61"/>
     </row>
     <row r="7" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A7" s="121"/>
-      <c r="B7" s="225"/>
-      <c r="C7" s="225"/>
+      <c r="A7" s="120"/>
+      <c r="B7" s="232">
+        <f>RESUMEN!H58</f>
+        <v>1959024</v>
+      </c>
+      <c r="C7" s="232"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
-      <c r="F7" s="115"/>
-      <c r="G7" s="115"/>
-      <c r="H7" s="115"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="115"/>
-      <c r="K7" s="115"/>
+      <c r="F7" s="114"/>
+      <c r="G7" s="114"/>
+      <c r="H7" s="114"/>
+      <c r="I7" s="114"/>
+      <c r="J7" s="114"/>
+      <c r="K7" s="114"/>
       <c r="L7" s="61"/>
       <c r="M7" s="61"/>
       <c r="N7" s="61"/>
     </row>
     <row r="8" spans="1:14" ht="53.25" customHeight="1" thickBot="1">
-      <c r="A8" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="110" t="s">
+      <c r="A8" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="111" t="s">
+      <c r="C8" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="112" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" s="110" t="s">
+      <c r="D8" s="111" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="113" t="s">
+      <c r="F8" s="112" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="113" t="s">
+      <c r="G8" s="112" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="113" t="s">
+      <c r="H8" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="113" t="s">
-        <v>143</v>
-      </c>
-      <c r="J8" s="113" t="s">
+      <c r="I8" s="112" t="s">
+        <v>142</v>
+      </c>
+      <c r="J8" s="112" t="s">
         <v>65</v>
       </c>
-      <c r="K8" s="127" t="s">
-        <v>131</v>
-      </c>
-      <c r="L8" s="110" t="s">
+      <c r="K8" s="126" t="s">
+        <v>130</v>
+      </c>
+      <c r="L8" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="M8" s="110" t="s">
-        <v>144</v>
-      </c>
-      <c r="N8" s="114" t="s">
+      <c r="M8" s="109" t="s">
+        <v>160</v>
+      </c>
+      <c r="N8" s="113" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
-      <c r="A9" s="173">
+      <c r="A9" s="172">
         <v>1</v>
       </c>
-      <c r="B9" s="169" t="s">
+      <c r="B9" s="168" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="170" t="s">
+      <c r="C9" s="169" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="170" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" s="171">
+      <c r="D9" s="169" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="170">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="F9" s="99">
+      <c r="F9" s="98">
         <v>593165.56411332928</v>
       </c>
-      <c r="G9" s="243"/>
+      <c r="G9" s="237">
+        <f>F9</f>
+        <v>593165.56411332928</v>
+      </c>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
-        <v>593165.56411332928</v>
+        <v>0</v>
       </c>
       <c r="I9" s="68">
         <f>H9*3.7%</f>
-        <v>21947.125872193188</v>
+        <v>0</v>
       </c>
       <c r="J9" s="68">
         <f>IF(G9&gt;F9,G9-F9,0)</f>
@@ -3826,19 +3870,19 @@
       </c>
       <c r="K9" s="68">
         <f>F$4*E9</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="172">
+        <v>4278.9059999999999</v>
+      </c>
+      <c r="L9" s="171">
         <f>B$5*E9</f>
-        <v>126775.576575</v>
-      </c>
-      <c r="M9" s="172">
+        <v>125593.48161</v>
+      </c>
+      <c r="M9" s="171">
         <f>B$7*E9</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="172">
+        <v>79340.472000000009</v>
+      </c>
+      <c r="N9" s="171">
         <f>H9+I9-J9+K9+L9+M9</f>
-        <v>741888.26656052237</v>
+        <v>209212.85961000001</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -3848,17 +3892,17 @@
       <c r="B10" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="93" t="s">
+      <c r="C10" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="93"/>
+      <c r="D10" s="92"/>
       <c r="E10" s="45">
         <v>6.4799999999999996E-2</v>
       </c>
       <c r="F10" s="17">
         <v>209002.56011999998</v>
       </c>
-      <c r="G10" s="241">
+      <c r="G10" s="238">
         <f>F10</f>
         <v>209002.56011999998</v>
       </c>
@@ -3876,41 +3920,41 @@
       </c>
       <c r="K10" s="24">
         <f t="shared" ref="K10:K31" si="2">F$4*E10</f>
-        <v>0</v>
+        <v>6846.2495999999992</v>
       </c>
       <c r="L10" s="25">
         <f t="shared" ref="L10:L31" si="3">B$5*E10</f>
-        <v>202840.92251999999</v>
+        <v>200949.570576</v>
       </c>
       <c r="M10" s="25">
         <f t="shared" ref="M10:M31" si="4">B$7*E10</f>
-        <v>0</v>
+        <v>126944.7552</v>
       </c>
       <c r="N10" s="25">
         <f t="shared" ref="N10:N31" si="5">H10+I10-J10+K10+L10+M10</f>
-        <v>202840.92251999999</v>
+        <v>334740.57537600002</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
-      <c r="A11" s="168">
+      <c r="A11" s="167">
         <v>3</v>
       </c>
-      <c r="B11" s="169" t="s">
+      <c r="B11" s="168" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="170" t="s">
+      <c r="C11" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="170" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" s="171">
+      <c r="D11" s="169" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="170">
         <v>4.82E-2</v>
       </c>
-      <c r="F11" s="99">
+      <c r="F11" s="98">
         <v>155423.56165999995</v>
       </c>
-      <c r="G11" s="241">
+      <c r="G11" s="238">
         <v>155430</v>
       </c>
       <c r="H11" s="68">
@@ -3927,68 +3971,68 @@
       </c>
       <c r="K11" s="68">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="172">
+        <v>5092.4264000000003</v>
+      </c>
+      <c r="L11" s="171">
         <f t="shared" si="3"/>
-        <v>150878.58742999999</v>
-      </c>
-      <c r="M11" s="172">
+        <v>149471.74848400001</v>
+      </c>
+      <c r="M11" s="171">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="172">
+        <v>94424.9568</v>
+      </c>
+      <c r="N11" s="171">
         <f>H11+I11-J11+K11+L11+M11+E7</f>
-        <v>150872.14908999993</v>
+        <v>248982.69334399997</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1">
-      <c r="A12" s="147">
+      <c r="A12" s="146">
         <v>4</v>
       </c>
-      <c r="B12" s="159" t="s">
+      <c r="B12" s="158" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="157" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="157" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" s="158">
+      <c r="C12" s="156" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="156" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="157">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="F12" s="151">
+      <c r="F12" s="150">
         <v>2604576.1956058415</v>
       </c>
-      <c r="G12" s="231"/>
-      <c r="H12" s="152">
+      <c r="G12" s="239"/>
+      <c r="H12" s="151">
         <f t="shared" si="0"/>
         <v>2604576.1956058415</v>
       </c>
-      <c r="I12" s="152">
+      <c r="I12" s="151">
         <f t="shared" si="6"/>
         <v>96369.319237416144</v>
       </c>
-      <c r="J12" s="152">
+      <c r="J12" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12" s="152">
+      <c r="K12" s="151">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="153">
+        <v>5652.3819999999996</v>
+      </c>
+      <c r="L12" s="152">
         <f t="shared" si="3"/>
-        <v>167468.971525</v>
-      </c>
-      <c r="M12" s="153">
+        <v>165907.43867</v>
+      </c>
+      <c r="M12" s="152">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="153">
+        <v>104807.784</v>
+      </c>
+      <c r="N12" s="152">
         <f t="shared" si="5"/>
-        <v>2868414.4863682576</v>
+        <v>2977313.1195132579</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
@@ -3998,17 +4042,17 @@
       <c r="B13" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="94" t="s">
+      <c r="C13" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="93"/>
+      <c r="D13" s="92"/>
       <c r="E13" s="45">
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="17">
         <v>124175.90377499998</v>
       </c>
-      <c r="G13" s="241">
+      <c r="G13" s="238">
         <f>F13</f>
         <v>124175.90377499998</v>
       </c>
@@ -4026,19 +4070,19 @@
       </c>
       <c r="K13" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4067.6019999999999</v>
       </c>
       <c r="L13" s="25">
         <f t="shared" si="3"/>
-        <v>120515.05427499999</v>
+        <v>119391.33437</v>
       </c>
       <c r="M13" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>75422.423999999999</v>
       </c>
       <c r="N13" s="25">
         <f t="shared" si="5"/>
-        <v>120515.05427499999</v>
+        <v>198881.36037000001</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
@@ -4048,11 +4092,11 @@
       <c r="B14" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="94" t="s">
+      <c r="C14" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="93" t="s">
-        <v>110</v>
+      <c r="D14" s="92" t="s">
+        <v>109</v>
       </c>
       <c r="E14" s="45">
         <v>3.5900000000000001E-2</v>
@@ -4060,7 +4104,7 @@
       <c r="F14" s="17">
         <v>115789.99858500001</v>
       </c>
-      <c r="G14" s="241">
+      <c r="G14" s="238">
         <f>F14</f>
         <v>115789.99858500001</v>
       </c>
@@ -4078,19 +4122,19 @@
       </c>
       <c r="K14" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3792.9068000000002</v>
       </c>
       <c r="L14" s="25">
         <f t="shared" si="3"/>
-        <v>112376.375285</v>
+        <v>111328.54295800001</v>
       </c>
       <c r="M14" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>70328.96160000001</v>
       </c>
       <c r="N14" s="25">
         <f t="shared" si="5"/>
-        <v>112376.375285</v>
+        <v>185450.41135800001</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -4100,11 +4144,11 @@
       <c r="B15" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="94" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="93" t="s">
-        <v>111</v>
+      <c r="C15" s="93" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15" s="92" t="s">
+        <v>110</v>
       </c>
       <c r="E15" s="45">
         <v>4.1399999999999999E-2</v>
@@ -4112,14 +4156,17 @@
       <c r="F15" s="17">
         <v>271999.41511616996</v>
       </c>
-      <c r="G15" s="241"/>
+      <c r="G15" s="238">
+        <f>F15</f>
+        <v>271999.41511616996</v>
+      </c>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
-        <v>271999.41511616996</v>
+        <v>0</v>
       </c>
       <c r="I15" s="24">
         <f t="shared" si="6"/>
-        <v>10063.978359298289</v>
+        <v>0</v>
       </c>
       <c r="J15" s="24">
         <f t="shared" si="1"/>
@@ -4127,19 +4174,19 @@
       </c>
       <c r="K15" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4373.9928</v>
       </c>
       <c r="L15" s="25">
         <f t="shared" si="3"/>
-        <v>129592.81160999999</v>
+        <v>128384.447868</v>
       </c>
       <c r="M15" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>81103.593599999993</v>
       </c>
       <c r="N15" s="25">
         <f t="shared" si="5"/>
-        <v>411656.20508546825</v>
+        <v>213862.03426799999</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -4149,11 +4196,11 @@
       <c r="B16" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="94" t="s">
+      <c r="C16" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="93" t="s">
-        <v>112</v>
+      <c r="D16" s="92" t="s">
+        <v>111</v>
       </c>
       <c r="E16" s="45">
         <v>5.3499999999999999E-2</v>
@@ -4161,7 +4208,7 @@
       <c r="F16" s="17">
         <v>172556.12602500001</v>
       </c>
-      <c r="G16" s="241">
+      <c r="G16" s="238">
         <f>F16</f>
         <v>172556.12602500001</v>
       </c>
@@ -4179,19 +4226,19 @@
       </c>
       <c r="K16" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5652.3819999999996</v>
       </c>
       <c r="L16" s="25">
         <f t="shared" si="3"/>
-        <v>167468.971525</v>
+        <v>165907.43867</v>
       </c>
       <c r="M16" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>104807.784</v>
       </c>
       <c r="N16" s="25">
         <f t="shared" si="5"/>
-        <v>167468.971525</v>
+        <v>276367.60467000003</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="15" customHeight="1">
@@ -4201,11 +4248,11 @@
       <c r="B17" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="93" t="s">
-        <v>113</v>
+      <c r="D17" s="92" t="s">
+        <v>112</v>
       </c>
       <c r="E17" s="45">
         <v>3.85E-2</v>
@@ -4213,7 +4260,7 @@
       <c r="F17" s="17">
         <v>124175.90377499998</v>
       </c>
-      <c r="G17" s="241">
+      <c r="G17" s="238">
         <f>F17+24</f>
         <v>124199.90377499998</v>
       </c>
@@ -4231,118 +4278,118 @@
       </c>
       <c r="K17" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4067.6019999999999</v>
       </c>
       <c r="L17" s="25">
         <f t="shared" si="3"/>
-        <v>120515.05427499999</v>
+        <v>119391.33437</v>
       </c>
       <c r="M17" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>75422.423999999999</v>
       </c>
       <c r="N17" s="25">
         <f t="shared" si="5"/>
-        <v>120491.05427499999</v>
+        <v>198857.36037000001</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1">
-      <c r="A18" s="232">
+      <c r="A18" s="181">
         <v>10</v>
       </c>
-      <c r="B18" s="233" t="s">
+      <c r="B18" s="182" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="234" t="s">
+      <c r="C18" s="183" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="235"/>
-      <c r="E18" s="236">
+      <c r="D18" s="184"/>
+      <c r="E18" s="185">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="F18" s="237">
+      <c r="F18" s="186">
         <v>514182.91629160853</v>
       </c>
-      <c r="G18" s="238">
-        <f>RESUMEN!H51+RESUMEN!H43+RESUMEN!H41</f>
-        <v>177500</v>
-      </c>
-      <c r="H18" s="239">
+      <c r="G18" s="240">
+        <f>359200</f>
+        <v>359200</v>
+      </c>
+      <c r="H18" s="187">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
-        <v>336682.91629160853</v>
-      </c>
-      <c r="I18" s="239">
+        <v>154982.91629160853</v>
+      </c>
+      <c r="I18" s="187">
         <f t="shared" si="6"/>
-        <v>12457.267902789517</v>
-      </c>
-      <c r="J18" s="239">
+        <v>5734.3679027895168</v>
+      </c>
+      <c r="J18" s="187">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="239">
+      <c r="K18" s="187">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="240">
+        <v>3792.9068000000002</v>
+      </c>
+      <c r="L18" s="188">
         <f t="shared" si="3"/>
-        <v>112376.375285</v>
-      </c>
-      <c r="M18" s="240">
+        <v>111328.54295800001</v>
+      </c>
+      <c r="M18" s="188">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="240">
+        <v>70328.96160000001</v>
+      </c>
+      <c r="N18" s="188">
         <f t="shared" si="5"/>
-        <v>461516.55947939807</v>
+        <v>346167.6955523981</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1">
-      <c r="A19" s="147">
+      <c r="A19" s="146">
         <v>11</v>
       </c>
-      <c r="B19" s="154" t="s">
+      <c r="B19" s="153" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="155" t="s">
+      <c r="C19" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="157" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" s="158">
+      <c r="D19" s="156" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="157">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F19" s="151">
+      <c r="F19" s="150">
         <v>1744190.8615374537</v>
       </c>
-      <c r="G19" s="231"/>
-      <c r="H19" s="152">
+      <c r="G19" s="239"/>
+      <c r="H19" s="151">
         <f t="shared" si="0"/>
         <v>1744190.8615374537</v>
       </c>
-      <c r="I19" s="152">
+      <c r="I19" s="151">
         <f t="shared" si="6"/>
         <v>64535.061876885797</v>
       </c>
-      <c r="J19" s="152">
+      <c r="J19" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K19" s="152">
+      <c r="K19" s="151">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="153">
+        <v>4373.9928</v>
+      </c>
+      <c r="L19" s="152">
         <f t="shared" si="3"/>
-        <v>129592.81160999999</v>
-      </c>
-      <c r="M19" s="153">
+        <v>128384.447868</v>
+      </c>
+      <c r="M19" s="152">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="153">
+        <v>81103.593599999993</v>
+      </c>
+      <c r="N19" s="152">
         <f t="shared" si="5"/>
-        <v>1938318.7350243395</v>
+        <v>2022587.9576823395</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1">
@@ -4352,11 +4399,11 @@
       <c r="B20" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="101" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" s="97" t="s">
-        <v>129</v>
+      <c r="C20" s="100" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="96" t="s">
+        <v>128</v>
       </c>
       <c r="E20" s="46">
         <v>5.3499999999999999E-2</v>
@@ -4364,7 +4411,7 @@
       <c r="F20" s="17">
         <v>172556.12602500001</v>
       </c>
-      <c r="G20" s="241">
+      <c r="G20" s="238">
         <f>172600</f>
         <v>172600</v>
       </c>
@@ -4382,70 +4429,70 @@
       </c>
       <c r="K20" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5652.3819999999996</v>
       </c>
       <c r="L20" s="25">
         <f t="shared" si="3"/>
-        <v>167468.971525</v>
+        <v>165907.43867</v>
       </c>
       <c r="M20" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>104807.784</v>
       </c>
       <c r="N20" s="25">
         <f t="shared" si="5"/>
-        <v>167425.09755000001</v>
+        <v>276323.73069500003</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1">
-      <c r="A21" s="147">
+      <c r="A21" s="146">
         <v>13</v>
       </c>
-      <c r="B21" s="154" t="s">
+      <c r="B21" s="153" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="155" t="s">
+      <c r="C21" s="154" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="155" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21" s="156">
+      <c r="D21" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="155">
         <v>3.85E-2</v>
       </c>
-      <c r="F21" s="151">
+      <c r="F21" s="150">
         <v>970537.78993118776</v>
       </c>
-      <c r="G21" s="242">
+      <c r="G21" s="241">
         <v>241030</v>
       </c>
-      <c r="H21" s="152">
+      <c r="H21" s="151">
         <f t="shared" si="0"/>
         <v>729507.78993118776</v>
       </c>
-      <c r="I21" s="152">
+      <c r="I21" s="151">
         <f t="shared" si="6"/>
         <v>26991.788227453952</v>
       </c>
-      <c r="J21" s="152">
+      <c r="J21" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K21" s="152">
+      <c r="K21" s="151">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="153">
+        <v>4067.6019999999999</v>
+      </c>
+      <c r="L21" s="152">
         <f t="shared" si="3"/>
-        <v>120515.05427499999</v>
-      </c>
-      <c r="M21" s="153">
+        <v>119391.33437</v>
+      </c>
+      <c r="M21" s="152">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="153">
+        <v>75422.423999999999</v>
+      </c>
+      <c r="N21" s="152">
         <f t="shared" si="5"/>
-        <v>877014.6324336417</v>
+        <v>955380.93852864171</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1">
@@ -4455,11 +4502,11 @@
       <c r="B22" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="94" t="s">
+      <c r="C22" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="94" t="s">
-        <v>115</v>
+      <c r="D22" s="93" t="s">
+        <v>114</v>
       </c>
       <c r="E22" s="47">
         <v>3.5900000000000001E-2</v>
@@ -4467,7 +4514,7 @@
       <c r="F22" s="17">
         <v>115789.99858500001</v>
       </c>
-      <c r="G22" s="241">
+      <c r="G22" s="238">
         <f>F22</f>
         <v>115789.99858500001</v>
       </c>
@@ -4485,19 +4532,19 @@
       </c>
       <c r="K22" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3792.9068000000002</v>
       </c>
       <c r="L22" s="25">
         <f t="shared" si="3"/>
-        <v>112376.375285</v>
+        <v>111328.54295800001</v>
       </c>
       <c r="M22" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>70328.96160000001</v>
       </c>
       <c r="N22" s="25">
         <f t="shared" si="5"/>
-        <v>112376.375285</v>
+        <v>185450.41135800001</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1">
@@ -4507,11 +4554,11 @@
       <c r="B23" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="95" t="s">
+      <c r="C23" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="95" t="s">
-        <v>116</v>
+      <c r="D23" s="94" t="s">
+        <v>115</v>
       </c>
       <c r="E23" s="48">
         <v>4.1399999999999999E-2</v>
@@ -4519,7 +4566,7 @@
       <c r="F23" s="17">
         <v>133529.41340999998</v>
       </c>
-      <c r="G23" s="241">
+      <c r="G23" s="238">
         <v>129592</v>
       </c>
       <c r="H23" s="24">
@@ -4536,19 +4583,19 @@
       </c>
       <c r="K23" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4373.9928</v>
       </c>
       <c r="L23" s="25">
         <f t="shared" si="3"/>
-        <v>129592.81160999999</v>
+        <v>128384.447868</v>
       </c>
       <c r="M23" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>81103.593599999993</v>
       </c>
       <c r="N23" s="25">
         <f t="shared" si="5"/>
-        <v>133675.90931616997</v>
+        <v>217945.13197416998</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1">
@@ -4558,17 +4605,17 @@
       <c r="B24" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="96" t="s">
+      <c r="C24" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="96"/>
+      <c r="D24" s="95"/>
       <c r="E24" s="49">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F24" s="17">
         <v>172556.12602500001</v>
       </c>
-      <c r="G24" s="241">
+      <c r="G24" s="238">
         <f>F24</f>
         <v>172556.12602500001</v>
       </c>
@@ -4586,19 +4633,19 @@
       </c>
       <c r="K24" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5652.3819999999996</v>
       </c>
       <c r="L24" s="25">
         <f t="shared" si="3"/>
-        <v>167468.971525</v>
+        <v>165907.43867</v>
       </c>
       <c r="M24" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>104807.784</v>
       </c>
       <c r="N24" s="25">
         <f t="shared" si="5"/>
-        <v>167468.971525</v>
+        <v>276367.60467000003</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="1" customFormat="1" ht="15.75" customHeight="1">
@@ -4608,11 +4655,11 @@
       <c r="B25" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="96" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" s="96" t="s">
-        <v>117</v>
+      <c r="C25" s="95" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="95" t="s">
+        <v>116</v>
       </c>
       <c r="E25" s="49">
         <v>3.85E-2</v>
@@ -4620,7 +4667,7 @@
       <c r="F25" s="17">
         <v>124175.90377499998</v>
       </c>
-      <c r="G25" s="241">
+      <c r="G25" s="238">
         <f>F25</f>
         <v>124175.90377499998</v>
       </c>
@@ -4638,19 +4685,19 @@
       </c>
       <c r="K25" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4067.6019999999999</v>
       </c>
       <c r="L25" s="25">
         <f t="shared" si="3"/>
-        <v>120515.05427499999</v>
+        <v>119391.33437</v>
       </c>
       <c r="M25" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>75422.423999999999</v>
       </c>
       <c r="N25" s="25">
         <f t="shared" si="5"/>
-        <v>120515.05427499999</v>
+        <v>198881.36037000001</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1">
@@ -4660,17 +4707,17 @@
       <c r="B26" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="96" t="s">
+      <c r="C26" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="96"/>
+      <c r="D26" s="95"/>
       <c r="E26" s="49">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F26" s="17">
         <v>115789.99858500001</v>
       </c>
-      <c r="G26" s="241">
+      <c r="G26" s="238">
         <f>F26</f>
         <v>115789.99858500001</v>
       </c>
@@ -4688,70 +4735,70 @@
       </c>
       <c r="K26" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3792.9068000000002</v>
       </c>
       <c r="L26" s="25">
         <f t="shared" si="3"/>
-        <v>112376.375285</v>
+        <v>111328.54295800001</v>
       </c>
       <c r="M26" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>70328.96160000001</v>
       </c>
       <c r="N26" s="25">
         <f t="shared" si="5"/>
-        <v>112376.375285</v>
+        <v>185450.41135800001</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1">
-      <c r="A27" s="147">
+      <c r="A27" s="146">
         <v>19</v>
       </c>
-      <c r="B27" s="148" t="s">
+      <c r="B27" s="147" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="149" t="s">
+      <c r="C27" s="148" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="149" t="s">
-        <v>130</v>
-      </c>
-      <c r="E27" s="150">
+      <c r="D27" s="148" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" s="149">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F27" s="151">
+      <c r="F27" s="150">
         <v>2688223.6303953365</v>
       </c>
-      <c r="G27" s="231">
+      <c r="G27" s="239">
         <v>133530</v>
       </c>
-      <c r="H27" s="174">
+      <c r="H27" s="173">
         <f t="shared" si="0"/>
         <v>2554693.6303953365</v>
       </c>
-      <c r="I27" s="152">
+      <c r="I27" s="151">
         <f t="shared" si="6"/>
         <v>94523.664324627462</v>
       </c>
-      <c r="J27" s="152">
+      <c r="J27" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K27" s="152">
+      <c r="K27" s="151">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="153">
+        <v>4373.9928</v>
+      </c>
+      <c r="L27" s="152">
         <f t="shared" si="3"/>
-        <v>129592.81160999999</v>
-      </c>
-      <c r="M27" s="153">
+        <v>128384.447868</v>
+      </c>
+      <c r="M27" s="152">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N27" s="153">
+        <v>81103.593599999993</v>
+      </c>
+      <c r="N27" s="152">
         <f t="shared" si="5"/>
-        <v>2778810.106329964</v>
+        <v>2863079.3289879635</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="17.25" customHeight="1">
@@ -4761,17 +4808,17 @@
       <c r="B28" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="96" t="s">
+      <c r="C28" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="96"/>
+      <c r="D28" s="95"/>
       <c r="E28" s="49">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
         <v>781282.18712432007</v>
       </c>
-      <c r="G28" s="241"/>
+      <c r="G28" s="238"/>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
         <v>781282.18712432007</v>
@@ -4787,15 +4834,15 @@
       <c r="K28" s="24"/>
       <c r="L28" s="25">
         <f t="shared" si="3"/>
-        <v>167468.971525</v>
+        <v>165907.43867</v>
       </c>
       <c r="M28" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>104807.784</v>
       </c>
       <c r="N28" s="25">
         <f t="shared" si="5"/>
-        <v>977658.59957292001</v>
+        <v>1080904.8507179199</v>
       </c>
       <c r="O28" s="7"/>
     </row>
@@ -4806,17 +4853,17 @@
       <c r="B29" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="96" t="s">
-        <v>104</v>
-      </c>
-      <c r="D29" s="96"/>
+      <c r="C29" s="95" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29" s="95"/>
       <c r="E29" s="49">
         <v>3.85E-2</v>
       </c>
       <c r="F29" s="17">
         <v>124175.90377499998</v>
       </c>
-      <c r="G29" s="241">
+      <c r="G29" s="238">
         <f>F29+24</f>
         <v>124199.90377499998</v>
       </c>
@@ -4834,19 +4881,19 @@
       </c>
       <c r="K29" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4067.6019999999999</v>
       </c>
       <c r="L29" s="25">
         <f t="shared" si="3"/>
-        <v>120515.05427499999</v>
+        <v>119391.33437</v>
       </c>
       <c r="M29" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>75422.423999999999</v>
       </c>
       <c r="N29" s="25">
         <f t="shared" si="5"/>
-        <v>120491.05427499999</v>
+        <v>198857.36037000001</v>
       </c>
       <c r="O29" s="7"/>
     </row>
@@ -4857,11 +4904,11 @@
       <c r="B30" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="96" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" s="96" t="s">
-        <v>134</v>
+      <c r="C30" s="95" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" s="95" t="s">
+        <v>133</v>
       </c>
       <c r="E30" s="49">
         <v>3.5900000000000001E-2</v>
@@ -4869,7 +4916,7 @@
       <c r="F30" s="17">
         <v>115789.99858500001</v>
       </c>
-      <c r="G30" s="241">
+      <c r="G30" s="238">
         <f>F30</f>
         <v>115789.99858500001</v>
       </c>
@@ -4887,19 +4934,19 @@
       </c>
       <c r="K30" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3792.9068000000002</v>
       </c>
       <c r="L30" s="25">
         <f t="shared" si="3"/>
-        <v>112376.375285</v>
+        <v>111328.54295800001</v>
       </c>
       <c r="M30" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>70328.96160000001</v>
       </c>
       <c r="N30" s="25">
         <f t="shared" si="5"/>
-        <v>112376.375285</v>
+        <v>185450.41135800001</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15" customHeight="1">
@@ -4909,17 +4956,17 @@
       <c r="B31" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="96" t="s">
+      <c r="C31" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="96"/>
+      <c r="D31" s="95"/>
       <c r="E31" s="49">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F31" s="17">
         <v>133529.41340999998</v>
       </c>
-      <c r="G31" s="241">
+      <c r="G31" s="238">
         <f>F31</f>
         <v>133529.41340999998</v>
       </c>
@@ -4937,19 +4984,19 @@
       </c>
       <c r="K31" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4373.9928</v>
       </c>
       <c r="L31" s="25">
         <f t="shared" si="3"/>
-        <v>129592.81160999999</v>
+        <v>128384.447868</v>
       </c>
       <c r="M31" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>81103.593599999993</v>
       </c>
       <c r="N31" s="25">
         <f t="shared" si="5"/>
-        <v>129592.81160999999</v>
+        <v>213862.03426799999</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15.75">
@@ -4964,151 +5011,151 @@
         <f>SUM(E9:E31)</f>
         <v>1</v>
       </c>
-      <c r="F32" s="100">
+      <c r="F32" s="99">
         <f>SUM(F9:F31)</f>
         <v>12277175.496230245</v>
       </c>
-      <c r="G32" s="100">
+      <c r="G32" s="99">
         <f>SUM(G9:G31)</f>
-        <v>2657237.8350200001</v>
-      </c>
-      <c r="H32" s="126">
+        <v>3704102.8142494997</v>
+      </c>
+      <c r="H32" s="125">
         <f>SUM(H9:H31)</f>
-        <v>9620035.9735252466</v>
+        <v>8573170.9942957461</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>355941.33102043415</v>
-      </c>
-      <c r="J32" s="100">
+        <v>317207.32678894268</v>
+      </c>
+      <c r="J32" s="99">
         <f t="shared" ref="J32" si="7">SUM(J9:J31)</f>
         <v>98.31231500004651</v>
       </c>
-      <c r="K32" s="91">
+      <c r="K32" s="90">
         <f>SUM(K9:K31)</f>
-        <v>0</v>
+        <v>99999.617999999959</v>
       </c>
       <c r="L32" s="54">
         <f>SUM(L9:L31)</f>
-        <v>3130261.1500000004</v>
-      </c>
-      <c r="M32" s="91">
+        <v>3101073.62</v>
+      </c>
+      <c r="M32" s="90">
         <f>SUM(M9:M31)</f>
-        <v>0</v>
+        <v>1959024.0000000002</v>
       </c>
       <c r="N32" s="54">
         <f>SUM(N9:N31)</f>
-        <v>13106140.14223068</v>
+        <v>14050377.246769693</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:14" hidden="1">
-      <c r="B34" s="224"/>
-      <c r="C34" s="224"/>
-      <c r="D34" s="224"/>
-      <c r="E34" s="224"/>
-      <c r="F34" s="224"/>
-      <c r="G34" s="224"/>
-      <c r="H34" s="224"/>
-      <c r="I34" s="224"/>
-      <c r="J34" s="224"/>
-      <c r="K34" s="224"/>
-      <c r="L34" s="224"/>
-      <c r="M34" s="224"/>
-      <c r="N34" s="224"/>
+      <c r="B34" s="231"/>
+      <c r="C34" s="231"/>
+      <c r="D34" s="231"/>
+      <c r="E34" s="231"/>
+      <c r="F34" s="231"/>
+      <c r="G34" s="231"/>
+      <c r="H34" s="231"/>
+      <c r="I34" s="231"/>
+      <c r="J34" s="231"/>
+      <c r="K34" s="231"/>
+      <c r="L34" s="231"/>
+      <c r="M34" s="231"/>
+      <c r="N34" s="231"/>
     </row>
     <row r="35" spans="1:14" hidden="1">
-      <c r="B35" s="224"/>
-      <c r="C35" s="224"/>
-      <c r="D35" s="224"/>
-      <c r="E35" s="224"/>
-      <c r="F35" s="224"/>
-      <c r="G35" s="224"/>
-      <c r="H35" s="224"/>
-      <c r="I35" s="224"/>
-      <c r="J35" s="224"/>
-      <c r="K35" s="224"/>
-      <c r="L35" s="224"/>
-      <c r="M35" s="224"/>
-      <c r="N35" s="224"/>
+      <c r="B35" s="231"/>
+      <c r="C35" s="231"/>
+      <c r="D35" s="231"/>
+      <c r="E35" s="231"/>
+      <c r="F35" s="231"/>
+      <c r="G35" s="231"/>
+      <c r="H35" s="231"/>
+      <c r="I35" s="231"/>
+      <c r="J35" s="231"/>
+      <c r="K35" s="231"/>
+      <c r="L35" s="231"/>
+      <c r="M35" s="231"/>
+      <c r="N35" s="231"/>
     </row>
     <row r="36" spans="1:14" hidden="1">
-      <c r="B36" s="224"/>
-      <c r="C36" s="224"/>
-      <c r="D36" s="224"/>
-      <c r="E36" s="224"/>
-      <c r="F36" s="224"/>
-      <c r="G36" s="224"/>
-      <c r="H36" s="224"/>
-      <c r="I36" s="224"/>
-      <c r="J36" s="224"/>
-      <c r="K36" s="224"/>
-      <c r="L36" s="224"/>
-      <c r="M36" s="224"/>
-      <c r="N36" s="224"/>
+      <c r="B36" s="231"/>
+      <c r="C36" s="231"/>
+      <c r="D36" s="231"/>
+      <c r="E36" s="231"/>
+      <c r="F36" s="231"/>
+      <c r="G36" s="231"/>
+      <c r="H36" s="231"/>
+      <c r="I36" s="231"/>
+      <c r="J36" s="231"/>
+      <c r="K36" s="231"/>
+      <c r="L36" s="231"/>
+      <c r="M36" s="231"/>
+      <c r="N36" s="231"/>
     </row>
     <row r="37" spans="1:14" hidden="1">
-      <c r="B37" s="224"/>
-      <c r="C37" s="224"/>
-      <c r="D37" s="224"/>
-      <c r="E37" s="224"/>
-      <c r="F37" s="224"/>
-      <c r="G37" s="224"/>
-      <c r="H37" s="224"/>
-      <c r="I37" s="224"/>
-      <c r="J37" s="224"/>
-      <c r="K37" s="224"/>
-      <c r="L37" s="224"/>
-      <c r="M37" s="224"/>
-      <c r="N37" s="224"/>
+      <c r="B37" s="231"/>
+      <c r="C37" s="231"/>
+      <c r="D37" s="231"/>
+      <c r="E37" s="231"/>
+      <c r="F37" s="231"/>
+      <c r="G37" s="231"/>
+      <c r="H37" s="231"/>
+      <c r="I37" s="231"/>
+      <c r="J37" s="231"/>
+      <c r="K37" s="231"/>
+      <c r="L37" s="231"/>
+      <c r="M37" s="231"/>
+      <c r="N37" s="231"/>
     </row>
     <row r="38" spans="1:14" hidden="1">
-      <c r="A38" s="226"/>
-      <c r="B38" s="226"/>
-      <c r="C38" s="226"/>
-      <c r="D38" s="226"/>
-      <c r="E38" s="226"/>
-      <c r="F38" s="226"/>
-      <c r="G38" s="226"/>
-      <c r="H38" s="226"/>
-      <c r="I38" s="226"/>
-      <c r="J38" s="226"/>
-      <c r="K38" s="226"/>
-      <c r="L38" s="226"/>
-      <c r="M38" s="226"/>
-      <c r="N38" s="226"/>
+      <c r="A38" s="233"/>
+      <c r="B38" s="233"/>
+      <c r="C38" s="233"/>
+      <c r="D38" s="233"/>
+      <c r="E38" s="233"/>
+      <c r="F38" s="233"/>
+      <c r="G38" s="233"/>
+      <c r="H38" s="233"/>
+      <c r="I38" s="233"/>
+      <c r="J38" s="233"/>
+      <c r="K38" s="233"/>
+      <c r="L38" s="233"/>
+      <c r="M38" s="233"/>
+      <c r="N38" s="233"/>
     </row>
     <row r="39" spans="1:14" hidden="1">
-      <c r="A39" s="226"/>
-      <c r="B39" s="226"/>
-      <c r="C39" s="226"/>
-      <c r="D39" s="226"/>
-      <c r="E39" s="226"/>
-      <c r="F39" s="226"/>
-      <c r="G39" s="226"/>
-      <c r="H39" s="226"/>
-      <c r="I39" s="226"/>
-      <c r="J39" s="226"/>
-      <c r="K39" s="226"/>
-      <c r="L39" s="226"/>
-      <c r="M39" s="226"/>
-      <c r="N39" s="226"/>
+      <c r="A39" s="233"/>
+      <c r="B39" s="233"/>
+      <c r="C39" s="233"/>
+      <c r="D39" s="233"/>
+      <c r="E39" s="233"/>
+      <c r="F39" s="233"/>
+      <c r="G39" s="233"/>
+      <c r="H39" s="233"/>
+      <c r="I39" s="233"/>
+      <c r="J39" s="233"/>
+      <c r="K39" s="233"/>
+      <c r="L39" s="233"/>
+      <c r="M39" s="233"/>
+      <c r="N39" s="233"/>
     </row>
     <row r="40" spans="1:14" hidden="1">
-      <c r="A40" s="226"/>
-      <c r="B40" s="226"/>
-      <c r="C40" s="226"/>
-      <c r="D40" s="226"/>
-      <c r="E40" s="226"/>
-      <c r="F40" s="226"/>
-      <c r="G40" s="226"/>
-      <c r="H40" s="226"/>
-      <c r="I40" s="226"/>
-      <c r="J40" s="226"/>
-      <c r="K40" s="226"/>
-      <c r="L40" s="226"/>
-      <c r="M40" s="226"/>
-      <c r="N40" s="226"/>
+      <c r="A40" s="233"/>
+      <c r="B40" s="233"/>
+      <c r="C40" s="233"/>
+      <c r="D40" s="233"/>
+      <c r="E40" s="233"/>
+      <c r="F40" s="233"/>
+      <c r="G40" s="233"/>
+      <c r="H40" s="233"/>
+      <c r="I40" s="233"/>
+      <c r="J40" s="233"/>
+      <c r="K40" s="233"/>
+      <c r="L40" s="233"/>
+      <c r="M40" s="233"/>
+      <c r="N40" s="233"/>
     </row>
     <row r="41" spans="1:14">
       <c r="N41" s="7"/>
@@ -5139,15 +5186,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="227" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="228"/>
-      <c r="C1" s="228"/>
-      <c r="D1" s="228"/>
-      <c r="E1" s="228"/>
-      <c r="F1" s="228"/>
-      <c r="G1" s="229"/>
+      <c r="A1" s="234" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="236"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -5156,7 +5203,7 @@
     <row r="3" spans="1:7">
       <c r="A3" s="57"/>
       <c r="B3" s="59" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G3" s="31"/>
     </row>
@@ -5178,7 +5225,7 @@
       <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="73"/>
+      <c r="A6" s="72"/>
       <c r="B6" s="64"/>
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
@@ -5199,14 +5246,14 @@
       <c r="C8" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="71" t="s">
         <v>2</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="75" t="s">
-        <v>98</v>
+      <c r="F8" s="74" t="s">
+        <v>97</v>
       </c>
       <c r="G8" s="29" t="s">
         <v>8</v>
@@ -5225,13 +5272,13 @@
       <c r="D9" s="45">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="E9" s="71">
+      <c r="E9" s="70">
         <f>B$4*D9</f>
         <v>16200</v>
       </c>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71" t="s">
-        <v>100</v>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5247,13 +5294,13 @@
       <c r="D10" s="45">
         <v>6.4799999999999996E-2</v>
       </c>
-      <c r="E10" s="71">
+      <c r="E10" s="70">
         <f t="shared" ref="E10:E31" si="0">B$4*D10</f>
         <v>25920</v>
       </c>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71" t="s">
-        <v>100</v>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5269,13 +5316,13 @@
       <c r="D11" s="45">
         <v>4.82E-2</v>
       </c>
-      <c r="E11" s="71">
+      <c r="E11" s="70">
         <f t="shared" si="0"/>
         <v>19280</v>
       </c>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71" t="s">
-        <v>100</v>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5291,13 +5338,13 @@
       <c r="D12" s="45">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="E12" s="71">
+      <c r="E12" s="70">
         <f t="shared" si="0"/>
         <v>21400</v>
       </c>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71" t="s">
-        <v>100</v>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5313,13 +5360,13 @@
       <c r="D13" s="45">
         <v>3.85E-2</v>
       </c>
-      <c r="E13" s="71">
+      <c r="E13" s="70">
         <f t="shared" si="0"/>
         <v>15400</v>
       </c>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71" t="s">
-        <v>100</v>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5335,15 +5382,15 @@
       <c r="D14" s="45">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="E14" s="71">
+      <c r="E14" s="70">
         <f t="shared" si="0"/>
         <v>14360</v>
       </c>
-      <c r="F14" s="71">
+      <c r="F14" s="70">
         <f>E14*6.3%</f>
         <v>904.68</v>
       </c>
-      <c r="G14" s="71">
+      <c r="G14" s="70">
         <f t="shared" ref="G14:G27" si="1">E14 +F14</f>
         <v>15264.68</v>
       </c>
@@ -5361,13 +5408,13 @@
       <c r="D15" s="45">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E15" s="71">
+      <c r="E15" s="70">
         <f t="shared" si="0"/>
         <v>16560</v>
       </c>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71" t="s">
-        <v>100</v>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -5383,13 +5430,13 @@
       <c r="D16" s="45">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="E16" s="71">
+      <c r="E16" s="70">
         <f t="shared" si="0"/>
         <v>21400</v>
       </c>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71" t="s">
-        <v>100</v>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -5405,13 +5452,13 @@
       <c r="D17" s="45">
         <v>3.85E-2</v>
       </c>
-      <c r="E17" s="71">
+      <c r="E17" s="70">
         <f t="shared" si="0"/>
         <v>15400</v>
       </c>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71" t="s">
-        <v>100</v>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5427,13 +5474,13 @@
       <c r="D18" s="45">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="E18" s="71">
+      <c r="E18" s="70">
         <f t="shared" si="0"/>
         <v>14360</v>
       </c>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71" t="s">
-        <v>100</v>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -5449,15 +5496,15 @@
       <c r="D19" s="45">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E19" s="71">
+      <c r="E19" s="70">
         <f t="shared" si="0"/>
         <v>16560</v>
       </c>
-      <c r="F19" s="71">
+      <c r="F19" s="70">
         <f>E19*6.3%</f>
         <v>1043.28</v>
       </c>
-      <c r="G19" s="71">
+      <c r="G19" s="70">
         <f t="shared" si="1"/>
         <v>17603.28</v>
       </c>
@@ -5475,13 +5522,13 @@
       <c r="D20" s="46">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="E20" s="71">
+      <c r="E20" s="70">
         <f t="shared" si="0"/>
         <v>21400</v>
       </c>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71" t="s">
-        <v>100</v>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -5497,13 +5544,13 @@
       <c r="D21" s="47">
         <v>3.85E-2</v>
       </c>
-      <c r="E21" s="71">
+      <c r="E21" s="70">
         <f t="shared" si="0"/>
         <v>15400</v>
       </c>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71" t="s">
-        <v>100</v>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -5519,13 +5566,13 @@
       <c r="D22" s="47">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="E22" s="71">
+      <c r="E22" s="70">
         <f t="shared" si="0"/>
         <v>14360</v>
       </c>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71" t="s">
-        <v>100</v>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -5541,13 +5588,13 @@
       <c r="D23" s="48">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E23" s="71">
+      <c r="E23" s="70">
         <f t="shared" si="0"/>
         <v>16560</v>
       </c>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71" t="s">
-        <v>100</v>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75">
@@ -5563,13 +5610,13 @@
       <c r="D24" s="49">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="E24" s="71">
+      <c r="E24" s="70">
         <f t="shared" si="0"/>
         <v>21400</v>
       </c>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71" t="s">
-        <v>100</v>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75">
@@ -5580,18 +5627,18 @@
         <v>56</v>
       </c>
       <c r="C25" s="65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D25" s="49">
         <v>3.85E-2</v>
       </c>
-      <c r="E25" s="71">
+      <c r="E25" s="70">
         <f t="shared" si="0"/>
         <v>15400</v>
       </c>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71" t="s">
-        <v>100</v>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75">
@@ -5607,13 +5654,13 @@
       <c r="D26" s="49">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="E26" s="71">
+      <c r="E26" s="70">
         <f t="shared" si="0"/>
         <v>14360</v>
       </c>
-      <c r="F26" s="71"/>
-      <c r="G26" s="71" t="s">
-        <v>100</v>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75">
@@ -5629,15 +5676,15 @@
       <c r="D27" s="49">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E27" s="71">
+      <c r="E27" s="70">
         <f t="shared" si="0"/>
         <v>16560</v>
       </c>
-      <c r="F27" s="71">
+      <c r="F27" s="70">
         <f>E27*6.3%</f>
         <v>1043.28</v>
       </c>
-      <c r="G27" s="71">
+      <c r="G27" s="70">
         <f t="shared" si="1"/>
         <v>17603.28</v>
       </c>
@@ -5655,13 +5702,13 @@
       <c r="D28" s="49">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="E28" s="71">
+      <c r="E28" s="70">
         <f t="shared" si="0"/>
         <v>21400</v>
       </c>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71" t="s">
-        <v>100</v>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75">
@@ -5677,13 +5724,13 @@
       <c r="D29" s="49">
         <v>3.85E-2</v>
       </c>
-      <c r="E29" s="71">
+      <c r="E29" s="70">
         <f t="shared" si="0"/>
         <v>15400</v>
       </c>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71" t="s">
-        <v>100</v>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75">
@@ -5699,13 +5746,13 @@
       <c r="D30" s="49">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="E30" s="71">
+      <c r="E30" s="70">
         <f t="shared" si="0"/>
         <v>14360</v>
       </c>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71" t="s">
-        <v>100</v>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.75">
@@ -5721,13 +5768,13 @@
       <c r="D31" s="49">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E31" s="71">
+      <c r="E31" s="70">
         <f t="shared" si="0"/>
         <v>16560</v>
       </c>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71" t="s">
-        <v>100</v>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75">
@@ -5749,11 +5796,11 @@
       <c r="G32" s="54"/>
     </row>
     <row r="34" spans="3:5" ht="13.5" customHeight="1">
-      <c r="C34" s="78" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="76"/>
-      <c r="E34" s="77">
+      <c r="C34" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" s="75"/>
+      <c r="E34" s="76">
         <f>SUMIF(G9:G31,"pago",E9:E31)</f>
         <v>352520</v>
       </c>
